--- a/data/verification/datastet_and_added_summarised/datastet_and_added_filled_raw/charite_dois_ids_distinct_v9.xlsx
+++ b/data/verification/datastet_and_added_summarised/datastet_and_added_filled_raw/charite_dois_ids_distinct_v9.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://charitede.sharepoint.com/sites/TeamOpenDataundForschungsdatenmanagement/Shared Documents/DCC analysis/datastet and added identifiers/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AVIHAY\git\DCC-v3\data\verification\datastet_and_added_summarised\datastet_and_added_filled_raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2590" documentId="11_57DF80A4F9203448D8892CCCE483C471B2B16C48" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0112AA1A-B760-433C-BE3E-82432C1584BC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3322BA5-DB1C-451A-957B-0E41A0843540}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,10 +28,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6809" uniqueCount="1408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6824" uniqueCount="1408">
   <si>
     <t>doi_datastet_and_added</t>
   </si>
@@ -3206,7 +3206,7 @@
     <t>err194147</t>
   </si>
   <si>
-    <t>ENA; no authors of dataset, but article indicates own data</t>
+    <t>ENA; no authors of dataset, but article indicates own data; 27.08.2025 AI: concluded as reuse</t>
   </si>
   <si>
     <t>10.1016/j.celrep.2020.108235</t>
@@ -3812,7 +3812,7 @@
     <t>ng00075</t>
   </si>
   <si>
-    <t>RECORD REMOVED?</t>
+    <t>dss NIAGADS</t>
   </si>
   <si>
     <t>NIAGADS Code of Conduct</t>
@@ -4332,7 +4332,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4346,12 +4346,9 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -4389,9 +4386,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4429,9 +4426,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4464,9 +4461,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4499,9 +4513,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4675,7 +4706,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P968"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -4738,7 +4768,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" hidden="1">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -4767,7 +4797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" hidden="1">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -4796,7 +4826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:16" hidden="1">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -5016,7 +5046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" hidden="1">
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -5048,7 +5078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16" hidden="1">
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -5080,7 +5110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16" hidden="1">
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -5112,7 +5142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:16" hidden="1">
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -5144,7 +5174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:16" hidden="1">
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -5173,7 +5203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16" hidden="1">
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -5202,7 +5232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:16" hidden="1">
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
         <v>46</v>
       </c>
@@ -5231,7 +5261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" hidden="1">
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
         <v>50</v>
       </c>
@@ -5248,7 +5278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:16" hidden="1">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>53</v>
       </c>
@@ -5277,7 +5307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:16" hidden="1">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>55</v>
       </c>
@@ -5447,7 +5477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:16" hidden="1">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>61</v>
       </c>
@@ -5526,7 +5556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:16" hidden="1">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>65</v>
       </c>
@@ -5543,7 +5573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:16" hidden="1">
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
         <v>67</v>
       </c>
@@ -5560,7 +5590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:16" hidden="1">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>68</v>
       </c>
@@ -5577,7 +5607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:16" hidden="1">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>69</v>
       </c>
@@ -5609,7 +5639,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:16" hidden="1">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>73</v>
       </c>
@@ -5638,7 +5668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16" hidden="1">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>75</v>
       </c>
@@ -5667,7 +5697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:16" hidden="1">
+    <row r="30" spans="1:16">
       <c r="A30" s="5" t="s">
         <v>77</v>
       </c>
@@ -5696,7 +5726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:16" hidden="1">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>79</v>
       </c>
@@ -5925,7 +5955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:15" hidden="1">
+    <row r="36" spans="1:15">
       <c r="A36" t="s">
         <v>89</v>
       </c>
@@ -5957,7 +5987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:15" hidden="1">
+    <row r="37" spans="1:15">
       <c r="A37" t="s">
         <v>92</v>
       </c>
@@ -5986,7 +6016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:15" hidden="1">
+    <row r="38" spans="1:15">
       <c r="A38" t="s">
         <v>95</v>
       </c>
@@ -6015,7 +6045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:15" hidden="1">
+    <row r="39" spans="1:15">
       <c r="A39" t="s">
         <v>98</v>
       </c>
@@ -6044,7 +6074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:15" hidden="1">
+    <row r="40" spans="1:15">
       <c r="A40" t="s">
         <v>101</v>
       </c>
@@ -6061,7 +6091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:15" hidden="1">
+    <row r="41" spans="1:15">
       <c r="A41" t="s">
         <v>103</v>
       </c>
@@ -6078,7 +6108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:15" hidden="1">
+    <row r="42" spans="1:15">
       <c r="A42" t="s">
         <v>105</v>
       </c>
@@ -6107,7 +6137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15" hidden="1">
+    <row r="43" spans="1:15">
       <c r="A43" t="s">
         <v>107</v>
       </c>
@@ -6136,7 +6166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:15" hidden="1">
+    <row r="44" spans="1:15">
       <c r="A44" t="s">
         <v>109</v>
       </c>
@@ -6165,7 +6195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15" hidden="1">
+    <row r="45" spans="1:15">
       <c r="A45" t="s">
         <v>111</v>
       </c>
@@ -6194,7 +6224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1">
+    <row r="46" spans="1:15">
       <c r="A46" t="s">
         <v>111</v>
       </c>
@@ -6270,7 +6300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:15" hidden="1">
+    <row r="48" spans="1:15">
       <c r="A48" t="s">
         <v>107</v>
       </c>
@@ -6299,7 +6329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15" hidden="1">
+    <row r="49" spans="1:15">
       <c r="A49" t="s">
         <v>75</v>
       </c>
@@ -6316,7 +6346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:15" hidden="1">
+    <row r="50" spans="1:15">
       <c r="A50" t="s">
         <v>118</v>
       </c>
@@ -6345,7 +6375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1">
+    <row r="51" spans="1:15">
       <c r="A51" s="5" t="s">
         <v>118</v>
       </c>
@@ -6374,7 +6404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15" hidden="1">
+    <row r="52" spans="1:15">
       <c r="A52" t="s">
         <v>69</v>
       </c>
@@ -6391,7 +6421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:15" hidden="1">
+    <row r="53" spans="1:15">
       <c r="A53" t="s">
         <v>123</v>
       </c>
@@ -6455,7 +6485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:15" hidden="1">
+    <row r="55" spans="1:15">
       <c r="A55" t="s">
         <v>127</v>
       </c>
@@ -6487,7 +6517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:15" hidden="1">
+    <row r="56" spans="1:15">
       <c r="A56" t="s">
         <v>129</v>
       </c>
@@ -6507,7 +6537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:15" hidden="1">
+    <row r="57" spans="1:15">
       <c r="A57" t="s">
         <v>131</v>
       </c>
@@ -6527,7 +6557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:15" hidden="1">
+    <row r="58" spans="1:15">
       <c r="A58" t="s">
         <v>133</v>
       </c>
@@ -6544,7 +6574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:15" hidden="1">
+    <row r="59" spans="1:15">
       <c r="A59" t="s">
         <v>134</v>
       </c>
@@ -6573,7 +6603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:15" hidden="1">
+    <row r="60" spans="1:15">
       <c r="A60" t="s">
         <v>136</v>
       </c>
@@ -6649,7 +6679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:15" hidden="1">
+    <row r="62" spans="1:15">
       <c r="A62" t="s">
         <v>138</v>
       </c>
@@ -6666,7 +6696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:15" hidden="1">
+    <row r="63" spans="1:15">
       <c r="A63" t="s">
         <v>140</v>
       </c>
@@ -6695,7 +6725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:15" hidden="1">
+    <row r="64" spans="1:15">
       <c r="A64" t="s">
         <v>142</v>
       </c>
@@ -6724,7 +6754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:15" hidden="1">
+    <row r="65" spans="1:15">
       <c r="A65" t="s">
         <v>134</v>
       </c>
@@ -6741,7 +6771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:15" hidden="1">
+    <row r="66" spans="1:15">
       <c r="A66" s="5" t="s">
         <v>144</v>
       </c>
@@ -6770,7 +6800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:15" hidden="1">
+    <row r="67" spans="1:15">
       <c r="A67" t="s">
         <v>146</v>
       </c>
@@ -6799,7 +6829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:15" hidden="1">
+    <row r="68" spans="1:15">
       <c r="A68" t="s">
         <v>148</v>
       </c>
@@ -6828,7 +6858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:15" hidden="1">
+    <row r="69" spans="1:15">
       <c r="A69" t="s">
         <v>150</v>
       </c>
@@ -6845,7 +6875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:15" hidden="1">
+    <row r="70" spans="1:15">
       <c r="A70" t="s">
         <v>152</v>
       </c>
@@ -6862,7 +6892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:15" hidden="1">
+    <row r="71" spans="1:15">
       <c r="A71" t="s">
         <v>153</v>
       </c>
@@ -6879,7 +6909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:15" hidden="1">
+    <row r="72" spans="1:15">
       <c r="A72" t="s">
         <v>146</v>
       </c>
@@ -6896,7 +6926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:15" hidden="1">
+    <row r="73" spans="1:15">
       <c r="A73" t="s">
         <v>156</v>
       </c>
@@ -6925,7 +6955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:15" hidden="1">
+    <row r="74" spans="1:15">
       <c r="A74" t="s">
         <v>158</v>
       </c>
@@ -6954,7 +6984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:15" hidden="1">
+    <row r="75" spans="1:15">
       <c r="A75" t="s">
         <v>160</v>
       </c>
@@ -6983,7 +7013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:15" hidden="1">
+    <row r="76" spans="1:15">
       <c r="A76" t="s">
         <v>148</v>
       </c>
@@ -7000,7 +7030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:15" hidden="1">
+    <row r="77" spans="1:15">
       <c r="A77" t="s">
         <v>163</v>
       </c>
@@ -7076,7 +7106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:15" hidden="1">
+    <row r="79" spans="1:15">
       <c r="A79" t="s">
         <v>167</v>
       </c>
@@ -7105,7 +7135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:15" hidden="1">
+    <row r="80" spans="1:15">
       <c r="A80" t="s">
         <v>169</v>
       </c>
@@ -7134,7 +7164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:15" hidden="1">
+    <row r="81" spans="1:15">
       <c r="A81" t="s">
         <v>138</v>
       </c>
@@ -7151,7 +7181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:15" hidden="1">
+    <row r="82" spans="1:15">
       <c r="A82" t="s">
         <v>172</v>
       </c>
@@ -7168,7 +7198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:15" hidden="1">
+    <row r="83" spans="1:15">
       <c r="A83" t="s">
         <v>174</v>
       </c>
@@ -7197,7 +7227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:15" hidden="1">
+    <row r="84" spans="1:15">
       <c r="A84" t="s">
         <v>167</v>
       </c>
@@ -7214,7 +7244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:15" hidden="1">
+    <row r="85" spans="1:15">
       <c r="A85" t="s">
         <v>146</v>
       </c>
@@ -7243,7 +7273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:15" hidden="1">
+    <row r="86" spans="1:15">
       <c r="A86" t="s">
         <v>140</v>
       </c>
@@ -7260,7 +7290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:15" hidden="1">
+    <row r="87" spans="1:15">
       <c r="A87" t="s">
         <v>142</v>
       </c>
@@ -7277,7 +7307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:15" hidden="1">
+    <row r="88" spans="1:15">
       <c r="A88" t="s">
         <v>179</v>
       </c>
@@ -7294,7 +7324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:15" hidden="1">
+    <row r="89" spans="1:15">
       <c r="A89" t="s">
         <v>131</v>
       </c>
@@ -7311,7 +7341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:15" hidden="1">
+    <row r="90" spans="1:15">
       <c r="A90" t="s">
         <v>181</v>
       </c>
@@ -7387,7 +7417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:15" hidden="1">
+    <row r="92" spans="1:15">
       <c r="A92" t="s">
         <v>146</v>
       </c>
@@ -7416,7 +7446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:15" hidden="1">
+    <row r="93" spans="1:15">
       <c r="A93" t="s">
         <v>125</v>
       </c>
@@ -7445,7 +7475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:15" hidden="1">
+    <row r="94" spans="1:15">
       <c r="A94" t="s">
         <v>187</v>
       </c>
@@ -7474,7 +7504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:15" hidden="1">
+    <row r="95" spans="1:15">
       <c r="A95" t="s">
         <v>95</v>
       </c>
@@ -7503,7 +7533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:15" hidden="1">
+    <row r="96" spans="1:15">
       <c r="A96" t="s">
         <v>160</v>
       </c>
@@ -7532,7 +7562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:15" hidden="1">
+    <row r="97" spans="1:15">
       <c r="A97" t="s">
         <v>190</v>
       </c>
@@ -7608,7 +7638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:15" hidden="1">
+    <row r="99" spans="1:15">
       <c r="A99" t="s">
         <v>193</v>
       </c>
@@ -7637,7 +7667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:15" hidden="1">
+    <row r="100" spans="1:15">
       <c r="A100" t="s">
         <v>125</v>
       </c>
@@ -7666,7 +7696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:15" hidden="1">
+    <row r="101" spans="1:15">
       <c r="A101" t="s">
         <v>196</v>
       </c>
@@ -7695,7 +7725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:15" hidden="1">
+    <row r="102" spans="1:15">
       <c r="A102" t="s">
         <v>198</v>
       </c>
@@ -7724,7 +7754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:15" hidden="1">
+    <row r="103" spans="1:15">
       <c r="A103" t="s">
         <v>200</v>
       </c>
@@ -7741,7 +7771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:15" hidden="1">
+    <row r="104" spans="1:15">
       <c r="A104" t="s">
         <v>202</v>
       </c>
@@ -7770,7 +7800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:15" hidden="1">
+    <row r="105" spans="1:15">
       <c r="A105" t="s">
         <v>204</v>
       </c>
@@ -7846,7 +7876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:15" hidden="1">
+    <row r="107" spans="1:15">
       <c r="A107" t="s">
         <v>208</v>
       </c>
@@ -7922,7 +7952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:15" hidden="1">
+    <row r="109" spans="1:15">
       <c r="A109" t="s">
         <v>213</v>
       </c>
@@ -7939,7 +7969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:15" hidden="1">
+    <row r="110" spans="1:15">
       <c r="A110" t="s">
         <v>190</v>
       </c>
@@ -7968,7 +7998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:15" hidden="1">
+    <row r="111" spans="1:15">
       <c r="A111" t="s">
         <v>148</v>
       </c>
@@ -7997,7 +8027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:15" hidden="1">
+    <row r="112" spans="1:15">
       <c r="A112" t="s">
         <v>217</v>
       </c>
@@ -8026,7 +8056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:15" hidden="1">
+    <row r="113" spans="1:15">
       <c r="A113" t="s">
         <v>219</v>
       </c>
@@ -8043,7 +8073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:15" hidden="1">
+    <row r="114" spans="1:15">
       <c r="A114" t="s">
         <v>221</v>
       </c>
@@ -8060,7 +8090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:15" hidden="1">
+    <row r="115" spans="1:15">
       <c r="A115" t="s">
         <v>160</v>
       </c>
@@ -8089,7 +8119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:15" hidden="1">
+    <row r="116" spans="1:15">
       <c r="A116" t="s">
         <v>200</v>
       </c>
@@ -8118,7 +8148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:15" hidden="1">
+    <row r="117" spans="1:15">
       <c r="A117" t="s">
         <v>225</v>
       </c>
@@ -8147,7 +8177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:15" hidden="1">
+    <row r="118" spans="1:15">
       <c r="A118" t="s">
         <v>227</v>
       </c>
@@ -8164,7 +8194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:15" hidden="1">
+    <row r="119" spans="1:15">
       <c r="A119" t="s">
         <v>229</v>
       </c>
@@ -8193,7 +8223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:15" hidden="1">
+    <row r="120" spans="1:15">
       <c r="A120" t="s">
         <v>231</v>
       </c>
@@ -8210,7 +8240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:15" hidden="1">
+    <row r="121" spans="1:15">
       <c r="A121" t="s">
         <v>103</v>
       </c>
@@ -8227,7 +8257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:15" hidden="1">
+    <row r="122" spans="1:15">
       <c r="A122" t="s">
         <v>234</v>
       </c>
@@ -8256,7 +8286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:15" hidden="1">
+    <row r="123" spans="1:15">
       <c r="A123" t="s">
         <v>217</v>
       </c>
@@ -8285,7 +8315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:15" hidden="1">
+    <row r="124" spans="1:15">
       <c r="A124" t="s">
         <v>237</v>
       </c>
@@ -8314,7 +8344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:15" hidden="1">
+    <row r="125" spans="1:15">
       <c r="A125" t="s">
         <v>239</v>
       </c>
@@ -8343,7 +8373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:15" hidden="1">
+    <row r="126" spans="1:15">
       <c r="A126" t="s">
         <v>208</v>
       </c>
@@ -8372,7 +8402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:15" hidden="1">
+    <row r="127" spans="1:15">
       <c r="A127" t="s">
         <v>107</v>
       </c>
@@ -8401,7 +8431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:15" hidden="1">
+    <row r="128" spans="1:15">
       <c r="A128" t="s">
         <v>243</v>
       </c>
@@ -8559,7 +8589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:15" hidden="1">
+    <row r="132" spans="1:15">
       <c r="A132" t="s">
         <v>250</v>
       </c>
@@ -8623,7 +8653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:15" hidden="1">
+    <row r="134" spans="1:15">
       <c r="A134" t="s">
         <v>125</v>
       </c>
@@ -8652,7 +8682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:15" hidden="1">
+    <row r="135" spans="1:15">
       <c r="A135" t="s">
         <v>69</v>
       </c>
@@ -8681,7 +8711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:15" hidden="1">
+    <row r="136" spans="1:15">
       <c r="A136" t="s">
         <v>125</v>
       </c>
@@ -8710,7 +8740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:15" hidden="1">
+    <row r="137" spans="1:15">
       <c r="A137" t="s">
         <v>256</v>
       </c>
@@ -8739,7 +8769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:15" hidden="1">
+    <row r="138" spans="1:15">
       <c r="A138" t="s">
         <v>243</v>
       </c>
@@ -8768,7 +8798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:15" hidden="1">
+    <row r="139" spans="1:15">
       <c r="A139" t="s">
         <v>138</v>
       </c>
@@ -8797,7 +8827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:15" hidden="1">
+    <row r="140" spans="1:15">
       <c r="A140" t="s">
         <v>260</v>
       </c>
@@ -8814,7 +8844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:15" hidden="1">
+    <row r="141" spans="1:15">
       <c r="A141" t="s">
         <v>262</v>
       </c>
@@ -8878,7 +8908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:15" hidden="1">
+    <row r="143" spans="1:15">
       <c r="A143" t="s">
         <v>237</v>
       </c>
@@ -8907,7 +8937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:15" hidden="1">
+    <row r="144" spans="1:15">
       <c r="A144" t="s">
         <v>160</v>
       </c>
@@ -8983,7 +9013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:15" hidden="1">
+    <row r="146" spans="1:15">
       <c r="A146" t="s">
         <v>160</v>
       </c>
@@ -9012,7 +9042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:15" hidden="1">
+    <row r="147" spans="1:15">
       <c r="A147" t="s">
         <v>234</v>
       </c>
@@ -9041,7 +9071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:15" hidden="1">
+    <row r="148" spans="1:15">
       <c r="A148" t="s">
         <v>125</v>
       </c>
@@ -9117,7 +9147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:15" hidden="1">
+    <row r="150" spans="1:15">
       <c r="A150" t="s">
         <v>273</v>
       </c>
@@ -9134,7 +9164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:15" hidden="1">
+    <row r="151" spans="1:15">
       <c r="A151" t="s">
         <v>275</v>
       </c>
@@ -9163,7 +9193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:15" hidden="1">
+    <row r="152" spans="1:15">
       <c r="A152" t="s">
         <v>239</v>
       </c>
@@ -9180,7 +9210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:15" hidden="1">
+    <row r="153" spans="1:15">
       <c r="A153" t="s">
         <v>278</v>
       </c>
@@ -9197,7 +9227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:15" hidden="1">
+    <row r="154" spans="1:15">
       <c r="A154" t="s">
         <v>213</v>
       </c>
@@ -9214,7 +9244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:15" hidden="1">
+    <row r="155" spans="1:15">
       <c r="A155" t="s">
         <v>279</v>
       </c>
@@ -9231,7 +9261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:15" hidden="1">
+    <row r="156" spans="1:15">
       <c r="A156" t="s">
         <v>271</v>
       </c>
@@ -9248,7 +9278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:15" hidden="1">
+    <row r="157" spans="1:15">
       <c r="A157" t="s">
         <v>281</v>
       </c>
@@ -9277,7 +9307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:15" hidden="1">
+    <row r="158" spans="1:15">
       <c r="A158" t="s">
         <v>278</v>
       </c>
@@ -9306,7 +9336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:15" hidden="1">
+    <row r="159" spans="1:15">
       <c r="A159" t="s">
         <v>283</v>
       </c>
@@ -9335,7 +9365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:15" hidden="1">
+    <row r="160" spans="1:15">
       <c r="A160" t="s">
         <v>284</v>
       </c>
@@ -9352,7 +9382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:15" hidden="1">
+    <row r="161" spans="1:15">
       <c r="A161" t="s">
         <v>286</v>
       </c>
@@ -9381,7 +9411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:15" hidden="1">
+    <row r="162" spans="1:15">
       <c r="A162" t="s">
         <v>229</v>
       </c>
@@ -9410,7 +9440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:15" hidden="1">
+    <row r="163" spans="1:15">
       <c r="A163" s="5" t="s">
         <v>289</v>
       </c>
@@ -9439,7 +9469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:15" hidden="1">
+    <row r="164" spans="1:15">
       <c r="A164" t="s">
         <v>291</v>
       </c>
@@ -9468,7 +9498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:15" hidden="1">
+    <row r="165" spans="1:15">
       <c r="A165" t="s">
         <v>217</v>
       </c>
@@ -9497,7 +9527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:15" hidden="1">
+    <row r="166" spans="1:15">
       <c r="A166" t="s">
         <v>217</v>
       </c>
@@ -9526,7 +9556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:15" hidden="1">
+    <row r="167" spans="1:15">
       <c r="A167" t="s">
         <v>294</v>
       </c>
@@ -9543,7 +9573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:15" hidden="1">
+    <row r="168" spans="1:15">
       <c r="A168" t="s">
         <v>291</v>
       </c>
@@ -9560,7 +9590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:15" hidden="1">
+    <row r="169" spans="1:15">
       <c r="A169" t="s">
         <v>294</v>
       </c>
@@ -9589,7 +9619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:15" hidden="1">
+    <row r="170" spans="1:15">
       <c r="A170" t="s">
         <v>291</v>
       </c>
@@ -9665,7 +9695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:15" hidden="1">
+    <row r="172" spans="1:15">
       <c r="A172" t="s">
         <v>299</v>
       </c>
@@ -9694,7 +9724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:15" hidden="1">
+    <row r="173" spans="1:15">
       <c r="A173" t="s">
         <v>294</v>
       </c>
@@ -9723,7 +9753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:15" hidden="1">
+    <row r="174" spans="1:15">
       <c r="A174" t="s">
         <v>286</v>
       </c>
@@ -9740,7 +9770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:15" hidden="1">
+    <row r="175" spans="1:15">
       <c r="A175" t="s">
         <v>303</v>
       </c>
@@ -9769,7 +9799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:15" hidden="1">
+    <row r="176" spans="1:15">
       <c r="A176" t="s">
         <v>305</v>
       </c>
@@ -9786,7 +9816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:15" hidden="1">
+    <row r="177" spans="1:15">
       <c r="A177" t="s">
         <v>291</v>
       </c>
@@ -9803,7 +9833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:15" hidden="1">
+    <row r="178" spans="1:15">
       <c r="A178" t="s">
         <v>286</v>
       </c>
@@ -9832,7 +9862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:15" hidden="1">
+    <row r="179" spans="1:15">
       <c r="A179" t="s">
         <v>308</v>
       </c>
@@ -9849,7 +9879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:15" hidden="1">
+    <row r="180" spans="1:15">
       <c r="A180" t="s">
         <v>291</v>
       </c>
@@ -9866,7 +9896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:15" hidden="1">
+    <row r="181" spans="1:15">
       <c r="A181" t="s">
         <v>310</v>
       </c>
@@ -9883,7 +9913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:15" hidden="1">
+    <row r="182" spans="1:15">
       <c r="A182" t="s">
         <v>312</v>
       </c>
@@ -9912,7 +9942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:15" hidden="1">
+    <row r="183" spans="1:15">
       <c r="A183" t="s">
         <v>291</v>
       </c>
@@ -9988,7 +10018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:15" hidden="1">
+    <row r="185" spans="1:15">
       <c r="A185" t="s">
         <v>291</v>
       </c>
@@ -10017,7 +10047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:15" hidden="1">
+    <row r="186" spans="1:15">
       <c r="A186" t="s">
         <v>317</v>
       </c>
@@ -10046,7 +10076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:15" hidden="1">
+    <row r="187" spans="1:15">
       <c r="A187" t="s">
         <v>319</v>
       </c>
@@ -10063,7 +10093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:15" hidden="1">
+    <row r="188" spans="1:15">
       <c r="A188" t="s">
         <v>237</v>
       </c>
@@ -10092,7 +10122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:15" hidden="1">
+    <row r="189" spans="1:15">
       <c r="A189" t="s">
         <v>291</v>
       </c>
@@ -10121,7 +10151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:15" hidden="1">
+    <row r="190" spans="1:15">
       <c r="A190" t="s">
         <v>323</v>
       </c>
@@ -10138,7 +10168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:15" hidden="1">
+    <row r="191" spans="1:15">
       <c r="A191" t="s">
         <v>325</v>
       </c>
@@ -10167,7 +10197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:15" hidden="1">
+    <row r="192" spans="1:15">
       <c r="A192" t="s">
         <v>243</v>
       </c>
@@ -10184,7 +10214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:15" hidden="1">
+    <row r="193" spans="1:15">
       <c r="A193" t="s">
         <v>312</v>
       </c>
@@ -10248,7 +10278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:15" hidden="1">
+    <row r="195" spans="1:15">
       <c r="A195" t="s">
         <v>299</v>
       </c>
@@ -10277,7 +10307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:15" hidden="1">
+    <row r="196" spans="1:15">
       <c r="A196" t="s">
         <v>331</v>
       </c>
@@ -10353,7 +10383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:15" hidden="1">
+    <row r="198" spans="1:15">
       <c r="A198" t="s">
         <v>148</v>
       </c>
@@ -10370,7 +10400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:15" hidden="1">
+    <row r="199" spans="1:15">
       <c r="A199" t="s">
         <v>335</v>
       </c>
@@ -10399,7 +10429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:15" hidden="1">
+    <row r="200" spans="1:15">
       <c r="A200" t="s">
         <v>337</v>
       </c>
@@ -10428,7 +10458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:15" hidden="1">
+    <row r="201" spans="1:15">
       <c r="A201" t="s">
         <v>291</v>
       </c>
@@ -10457,7 +10487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:15" hidden="1">
+    <row r="202" spans="1:15">
       <c r="A202" t="s">
         <v>208</v>
       </c>
@@ -10486,7 +10516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:15" hidden="1">
+    <row r="203" spans="1:15">
       <c r="A203" t="s">
         <v>291</v>
       </c>
@@ -10515,7 +10545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:15" hidden="1">
+    <row r="204" spans="1:15">
       <c r="A204" t="s">
         <v>342</v>
       </c>
@@ -10544,7 +10574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:15" hidden="1">
+    <row r="205" spans="1:15">
       <c r="A205" t="s">
         <v>308</v>
       </c>
@@ -10573,7 +10603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:15" hidden="1">
+    <row r="206" spans="1:15">
       <c r="A206" t="s">
         <v>344</v>
       </c>
@@ -10602,7 +10632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:15" hidden="1">
+    <row r="207" spans="1:15">
       <c r="A207" t="s">
         <v>346</v>
       </c>
@@ -10631,7 +10661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:15" hidden="1">
+    <row r="208" spans="1:15">
       <c r="A208" t="s">
         <v>98</v>
       </c>
@@ -10660,7 +10690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:15" hidden="1">
+    <row r="209" spans="1:15">
       <c r="A209" t="s">
         <v>158</v>
       </c>
@@ -10677,7 +10707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:15" hidden="1">
+    <row r="210" spans="1:15">
       <c r="A210" t="s">
         <v>350</v>
       </c>
@@ -10706,7 +10736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:15" hidden="1">
+    <row r="211" spans="1:15">
       <c r="A211" t="s">
         <v>352</v>
       </c>
@@ -10735,7 +10765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:15" hidden="1">
+    <row r="212" spans="1:15">
       <c r="A212" t="s">
         <v>354</v>
       </c>
@@ -10752,7 +10782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:15" hidden="1">
+    <row r="213" spans="1:15">
       <c r="A213" t="s">
         <v>234</v>
       </c>
@@ -10781,7 +10811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:15" hidden="1">
+    <row r="214" spans="1:15">
       <c r="A214" s="5" t="s">
         <v>86</v>
       </c>
@@ -10810,7 +10840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:15" hidden="1">
+    <row r="215" spans="1:15">
       <c r="A215" t="s">
         <v>358</v>
       </c>
@@ -10839,7 +10869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:15" hidden="1">
+    <row r="216" spans="1:15">
       <c r="A216" t="s">
         <v>360</v>
       </c>
@@ -10868,7 +10898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:15" hidden="1">
+    <row r="217" spans="1:15">
       <c r="A217" t="s">
         <v>362</v>
       </c>
@@ -10897,7 +10927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:15" hidden="1">
+    <row r="218" spans="1:15">
       <c r="A218" t="s">
         <v>364</v>
       </c>
@@ -10926,7 +10956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:15" hidden="1">
+    <row r="219" spans="1:15">
       <c r="A219" t="s">
         <v>286</v>
       </c>
@@ -10955,7 +10985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:15" hidden="1">
+    <row r="220" spans="1:15">
       <c r="A220" t="s">
         <v>367</v>
       </c>
@@ -10984,7 +11014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:15" hidden="1">
+    <row r="221" spans="1:15">
       <c r="A221" t="s">
         <v>196</v>
       </c>
@@ -11013,7 +11043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:15" hidden="1">
+    <row r="222" spans="1:15">
       <c r="A222" t="s">
         <v>370</v>
       </c>
@@ -11042,7 +11072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:15" hidden="1">
+    <row r="223" spans="1:15">
       <c r="A223" t="s">
         <v>234</v>
       </c>
@@ -11071,7 +11101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:15" hidden="1">
+    <row r="224" spans="1:15">
       <c r="A224" t="s">
         <v>125</v>
       </c>
@@ -11100,7 +11130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:15" hidden="1">
+    <row r="225" spans="1:15">
       <c r="A225" t="s">
         <v>373</v>
       </c>
@@ -11117,7 +11147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:15" hidden="1">
+    <row r="226" spans="1:15">
       <c r="A226" t="s">
         <v>375</v>
       </c>
@@ -11134,7 +11164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:15" hidden="1">
+    <row r="227" spans="1:15">
       <c r="A227" t="s">
         <v>376</v>
       </c>
@@ -11163,7 +11193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:15" hidden="1">
+    <row r="228" spans="1:15">
       <c r="A228" t="s">
         <v>378</v>
       </c>
@@ -11192,7 +11222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:15" hidden="1">
+    <row r="229" spans="1:15">
       <c r="A229" t="s">
         <v>379</v>
       </c>
@@ -11221,7 +11251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:15" hidden="1">
+    <row r="230" spans="1:15">
       <c r="A230" t="s">
         <v>380</v>
       </c>
@@ -11238,7 +11268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:15" hidden="1">
+    <row r="231" spans="1:15">
       <c r="A231" s="5" t="s">
         <v>382</v>
       </c>
@@ -11267,7 +11297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:15" hidden="1">
+    <row r="232" spans="1:15">
       <c r="A232" t="s">
         <v>358</v>
       </c>
@@ -11296,7 +11326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:15" hidden="1">
+    <row r="233" spans="1:15">
       <c r="A233" t="s">
         <v>360</v>
       </c>
@@ -11325,7 +11355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:15" hidden="1">
+    <row r="234" spans="1:15">
       <c r="A234" t="s">
         <v>167</v>
       </c>
@@ -11354,7 +11384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:15" hidden="1">
+    <row r="235" spans="1:15">
       <c r="A235" t="s">
         <v>387</v>
       </c>
@@ -11371,7 +11401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:15" hidden="1">
+    <row r="236" spans="1:15">
       <c r="A236" t="s">
         <v>389</v>
       </c>
@@ -11400,7 +11430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:15" hidden="1">
+    <row r="237" spans="1:15">
       <c r="A237" t="s">
         <v>138</v>
       </c>
@@ -11429,7 +11459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:15" hidden="1">
+    <row r="238" spans="1:15">
       <c r="A238" t="s">
         <v>358</v>
       </c>
@@ -11458,7 +11488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:15" hidden="1">
+    <row r="239" spans="1:15">
       <c r="A239" t="s">
         <v>231</v>
       </c>
@@ -11487,7 +11517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:15" hidden="1">
+    <row r="240" spans="1:15">
       <c r="A240" t="s">
         <v>73</v>
       </c>
@@ -11516,7 +11546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:15" hidden="1">
+    <row r="241" spans="1:15">
       <c r="A241" t="s">
         <v>196</v>
       </c>
@@ -11545,7 +11575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:15" hidden="1">
+    <row r="242" spans="1:15">
       <c r="A242" t="s">
         <v>396</v>
       </c>
@@ -11574,7 +11604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:15" hidden="1">
+    <row r="243" spans="1:15">
       <c r="A243" t="s">
         <v>358</v>
       </c>
@@ -11603,7 +11633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:15" hidden="1">
+    <row r="244" spans="1:15">
       <c r="A244" t="s">
         <v>399</v>
       </c>
@@ -11632,7 +11662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:15" hidden="1">
+    <row r="245" spans="1:15">
       <c r="A245" t="s">
         <v>401</v>
       </c>
@@ -11661,7 +11691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:15" hidden="1">
+    <row r="246" spans="1:15">
       <c r="A246" s="5" t="s">
         <v>387</v>
       </c>
@@ -11690,7 +11720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:15" hidden="1">
+    <row r="247" spans="1:15">
       <c r="A247" t="s">
         <v>404</v>
       </c>
@@ -11719,7 +11749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:15" hidden="1">
+    <row r="248" spans="1:15">
       <c r="A248" t="s">
         <v>360</v>
       </c>
@@ -11748,7 +11778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:15" hidden="1">
+    <row r="249" spans="1:15">
       <c r="A249" t="s">
         <v>231</v>
       </c>
@@ -11777,7 +11807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:15" hidden="1">
+    <row r="250" spans="1:15">
       <c r="A250" t="s">
         <v>408</v>
       </c>
@@ -11806,7 +11836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:15" hidden="1">
+    <row r="251" spans="1:15">
       <c r="A251" t="s">
         <v>358</v>
       </c>
@@ -11835,7 +11865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:15" hidden="1">
+    <row r="252" spans="1:15">
       <c r="A252" t="s">
         <v>231</v>
       </c>
@@ -11864,7 +11894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:15" hidden="1">
+    <row r="253" spans="1:15">
       <c r="A253" t="s">
         <v>160</v>
       </c>
@@ -11940,7 +11970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:15" hidden="1">
+    <row r="255" spans="1:15">
       <c r="A255" t="s">
         <v>231</v>
       </c>
@@ -11969,7 +11999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:15" hidden="1">
+    <row r="256" spans="1:15">
       <c r="A256" t="s">
         <v>144</v>
       </c>
@@ -11998,7 +12028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:15" hidden="1">
+    <row r="257" spans="1:15">
       <c r="A257" t="s">
         <v>286</v>
       </c>
@@ -12027,7 +12057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:15" hidden="1">
+    <row r="258" spans="1:15">
       <c r="A258" t="s">
         <v>344</v>
       </c>
@@ -12056,7 +12086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:15" hidden="1">
+    <row r="259" spans="1:15">
       <c r="A259" t="s">
         <v>136</v>
       </c>
@@ -12085,7 +12115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:15" hidden="1">
+    <row r="260" spans="1:15">
       <c r="A260" t="s">
         <v>420</v>
       </c>
@@ -12114,7 +12144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:15" hidden="1">
+    <row r="261" spans="1:15">
       <c r="A261" t="s">
         <v>362</v>
       </c>
@@ -12143,7 +12173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:15" hidden="1">
+    <row r="262" spans="1:15">
       <c r="A262" t="s">
         <v>234</v>
       </c>
@@ -12172,7 +12202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:15" hidden="1">
+    <row r="263" spans="1:15">
       <c r="A263" t="s">
         <v>346</v>
       </c>
@@ -12201,7 +12231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:15" hidden="1">
+    <row r="264" spans="1:15">
       <c r="A264" t="s">
         <v>217</v>
       </c>
@@ -12230,7 +12260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:15" hidden="1">
+    <row r="265" spans="1:15">
       <c r="A265" t="s">
         <v>89</v>
       </c>
@@ -12259,7 +12289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:15" hidden="1">
+    <row r="266" spans="1:15">
       <c r="A266" t="s">
         <v>426</v>
       </c>
@@ -12288,7 +12318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:15" hidden="1">
+    <row r="267" spans="1:15">
       <c r="A267" t="s">
         <v>428</v>
       </c>
@@ -12305,7 +12335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:15" hidden="1">
+    <row r="268" spans="1:15">
       <c r="A268" t="s">
         <v>430</v>
       </c>
@@ -12334,7 +12364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:15" s="6" customFormat="1" hidden="1">
+    <row r="269" spans="1:15" s="6" customFormat="1">
       <c r="A269" s="6" t="s">
         <v>432</v>
       </c>
@@ -12355,7 +12385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:15" hidden="1">
+    <row r="270" spans="1:15">
       <c r="A270" t="s">
         <v>247</v>
       </c>
@@ -12384,7 +12414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:15" hidden="1">
+    <row r="271" spans="1:15">
       <c r="A271" t="s">
         <v>325</v>
       </c>
@@ -12413,7 +12443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:15" hidden="1">
+    <row r="272" spans="1:15">
       <c r="A272" t="s">
         <v>360</v>
       </c>
@@ -12442,7 +12472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:15" hidden="1">
+    <row r="273" spans="1:15">
       <c r="A273" t="s">
         <v>231</v>
       </c>
@@ -12471,7 +12501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:15" hidden="1">
+    <row r="274" spans="1:15">
       <c r="A274" t="s">
         <v>438</v>
       </c>
@@ -12500,7 +12530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:15" hidden="1">
+    <row r="275" spans="1:15">
       <c r="A275" t="s">
         <v>440</v>
       </c>
@@ -12529,7 +12559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:15" hidden="1">
+    <row r="276" spans="1:15">
       <c r="A276" t="s">
         <v>346</v>
       </c>
@@ -12558,7 +12588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:15" hidden="1">
+    <row r="277" spans="1:15">
       <c r="A277" t="s">
         <v>442</v>
       </c>
@@ -12634,7 +12664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:15" hidden="1">
+    <row r="279" spans="1:15">
       <c r="A279" t="s">
         <v>234</v>
       </c>
@@ -12663,7 +12693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:15" hidden="1">
+    <row r="280" spans="1:15">
       <c r="A280" t="s">
         <v>346</v>
       </c>
@@ -12692,7 +12722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:15" hidden="1">
+    <row r="281" spans="1:15">
       <c r="A281" t="s">
         <v>440</v>
       </c>
@@ -12721,7 +12751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:15" hidden="1">
+    <row r="282" spans="1:15">
       <c r="A282" t="s">
         <v>234</v>
       </c>
@@ -12750,7 +12780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:15" hidden="1">
+    <row r="283" spans="1:15">
       <c r="A283" t="s">
         <v>346</v>
       </c>
@@ -12779,7 +12809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:15" hidden="1">
+    <row r="284" spans="1:15">
       <c r="A284" t="s">
         <v>387</v>
       </c>
@@ -12808,7 +12838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:15" hidden="1">
+    <row r="285" spans="1:15">
       <c r="A285" t="s">
         <v>231</v>
       </c>
@@ -12837,7 +12867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:15" hidden="1">
+    <row r="286" spans="1:15">
       <c r="A286" t="s">
         <v>125</v>
       </c>
@@ -12854,7 +12884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:15" hidden="1">
+    <row r="287" spans="1:15">
       <c r="A287" t="s">
         <v>451</v>
       </c>
@@ -12883,7 +12913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:15" hidden="1">
+    <row r="288" spans="1:15">
       <c r="A288" t="s">
         <v>387</v>
       </c>
@@ -13100,7 +13130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:15" hidden="1">
+    <row r="293" spans="1:15">
       <c r="A293" t="s">
         <v>217</v>
       </c>
@@ -13129,7 +13159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:15" hidden="1">
+    <row r="294" spans="1:15">
       <c r="A294" t="s">
         <v>460</v>
       </c>
@@ -13158,7 +13188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:15" hidden="1">
+    <row r="295" spans="1:15">
       <c r="A295" t="s">
         <v>462</v>
       </c>
@@ -13234,7 +13264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:15" hidden="1">
+    <row r="297" spans="1:15">
       <c r="A297" t="s">
         <v>465</v>
       </c>
@@ -13263,7 +13293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:15" hidden="1">
+    <row r="298" spans="1:15">
       <c r="A298" t="s">
         <v>467</v>
       </c>
@@ -13292,7 +13322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:15" hidden="1">
+    <row r="299" spans="1:15">
       <c r="A299" t="s">
         <v>144</v>
       </c>
@@ -13321,7 +13351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:15" hidden="1">
+    <row r="300" spans="1:15">
       <c r="A300" t="s">
         <v>438</v>
       </c>
@@ -13350,7 +13380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:15" hidden="1">
+    <row r="301" spans="1:15">
       <c r="A301" t="s">
         <v>396</v>
       </c>
@@ -13379,7 +13409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:15" hidden="1">
+    <row r="302" spans="1:15">
       <c r="A302" t="s">
         <v>399</v>
       </c>
@@ -13408,7 +13438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:15" hidden="1">
+    <row r="303" spans="1:15">
       <c r="A303" t="s">
         <v>404</v>
       </c>
@@ -13437,7 +13467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:15" hidden="1">
+    <row r="304" spans="1:15">
       <c r="A304" t="s">
         <v>440</v>
       </c>
@@ -13466,7 +13496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:15" hidden="1">
+    <row r="305" spans="1:15">
       <c r="A305" t="s">
         <v>404</v>
       </c>
@@ -13495,7 +13525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:15" hidden="1">
+    <row r="306" spans="1:15">
       <c r="A306" t="s">
         <v>475</v>
       </c>
@@ -13524,7 +13554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:15" hidden="1">
+    <row r="307" spans="1:15">
       <c r="A307" t="s">
         <v>477</v>
       </c>
@@ -13553,7 +13583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:15" hidden="1">
+    <row r="308" spans="1:15">
       <c r="A308" t="s">
         <v>190</v>
       </c>
@@ -13582,7 +13612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:15" hidden="1">
+    <row r="309" spans="1:15">
       <c r="A309" t="s">
         <v>286</v>
       </c>
@@ -13611,7 +13641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:15" hidden="1">
+    <row r="310" spans="1:15">
       <c r="A310" t="s">
         <v>420</v>
       </c>
@@ -13640,7 +13670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:15" hidden="1">
+    <row r="311" spans="1:15">
       <c r="A311" t="s">
         <v>389</v>
       </c>
@@ -13669,7 +13699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:15" hidden="1">
+    <row r="312" spans="1:15">
       <c r="A312" t="s">
         <v>243</v>
       </c>
@@ -13698,7 +13728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:15" hidden="1">
+    <row r="313" spans="1:15">
       <c r="A313" t="s">
         <v>160</v>
       </c>
@@ -13727,7 +13757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:15" hidden="1">
+    <row r="314" spans="1:15">
       <c r="A314" t="s">
         <v>286</v>
       </c>
@@ -13756,7 +13786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:15" hidden="1">
+    <row r="315" spans="1:15">
       <c r="A315" t="s">
         <v>408</v>
       </c>
@@ -13785,7 +13815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:15" hidden="1">
+    <row r="316" spans="1:15">
       <c r="A316" t="s">
         <v>109</v>
       </c>
@@ -13814,7 +13844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:15" hidden="1">
+    <row r="317" spans="1:15">
       <c r="A317" t="s">
         <v>325</v>
       </c>
@@ -13843,7 +13873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:15" hidden="1">
+    <row r="318" spans="1:15">
       <c r="A318" t="s">
         <v>485</v>
       </c>
@@ -13872,7 +13902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:15" hidden="1">
+    <row r="319" spans="1:15">
       <c r="A319" t="s">
         <v>428</v>
       </c>
@@ -13889,7 +13919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:15" hidden="1">
+    <row r="320" spans="1:15">
       <c r="A320" t="s">
         <v>428</v>
       </c>
@@ -13906,7 +13936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:15" hidden="1">
+    <row r="321" spans="1:15">
       <c r="A321" t="s">
         <v>442</v>
       </c>
@@ -13935,7 +13965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:15" hidden="1">
+    <row r="322" spans="1:15">
       <c r="A322" t="s">
         <v>247</v>
       </c>
@@ -13964,7 +13994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:15" hidden="1">
+    <row r="323" spans="1:15">
       <c r="A323" t="s">
         <v>399</v>
       </c>
@@ -13993,7 +14023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:15" hidden="1">
+    <row r="324" spans="1:15">
       <c r="A324" t="s">
         <v>442</v>
       </c>
@@ -14022,7 +14052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:15" hidden="1">
+    <row r="325" spans="1:15">
       <c r="A325" t="s">
         <v>387</v>
       </c>
@@ -14039,7 +14069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:15" hidden="1">
+    <row r="326" spans="1:15">
       <c r="A326" t="s">
         <v>160</v>
       </c>
@@ -14115,7 +14145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:15" hidden="1">
+    <row r="328" spans="1:15">
       <c r="A328" t="s">
         <v>495</v>
       </c>
@@ -14144,7 +14174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:15" hidden="1">
+    <row r="329" spans="1:15">
       <c r="A329" t="s">
         <v>430</v>
       </c>
@@ -14173,7 +14203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:15" s="6" customFormat="1" hidden="1">
+    <row r="330" spans="1:15" s="6" customFormat="1">
       <c r="A330" s="6" t="s">
         <v>432</v>
       </c>
@@ -14241,7 +14271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:15" hidden="1">
+    <row r="332" spans="1:15">
       <c r="A332" t="s">
         <v>500</v>
       </c>
@@ -14270,7 +14300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:15" hidden="1">
+    <row r="333" spans="1:15">
       <c r="A333" t="s">
         <v>502</v>
       </c>
@@ -14299,7 +14329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:15" hidden="1">
+    <row r="334" spans="1:15">
       <c r="A334" t="s">
         <v>399</v>
       </c>
@@ -14328,7 +14358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:15" hidden="1">
+    <row r="335" spans="1:15">
       <c r="A335" t="s">
         <v>505</v>
       </c>
@@ -14357,7 +14387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:15" hidden="1">
+    <row r="336" spans="1:15">
       <c r="A336" t="s">
         <v>438</v>
       </c>
@@ -14386,7 +14416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:15" hidden="1">
+    <row r="337" spans="1:15">
       <c r="A337" t="s">
         <v>420</v>
       </c>
@@ -14415,7 +14445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:15" hidden="1">
+    <row r="338" spans="1:15">
       <c r="A338" t="s">
         <v>509</v>
       </c>
@@ -14432,7 +14462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:15" hidden="1">
+    <row r="339" spans="1:15">
       <c r="A339" t="s">
         <v>148</v>
       </c>
@@ -14555,7 +14585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:15" hidden="1">
+    <row r="342" spans="1:15">
       <c r="A342" t="s">
         <v>515</v>
       </c>
@@ -14584,7 +14614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:15" hidden="1">
+    <row r="343" spans="1:15">
       <c r="A343" t="s">
         <v>148</v>
       </c>
@@ -14613,7 +14643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:15" hidden="1">
+    <row r="344" spans="1:15">
       <c r="A344" t="s">
         <v>518</v>
       </c>
@@ -14642,7 +14672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:15" hidden="1">
+    <row r="345" spans="1:15">
       <c r="A345" t="s">
         <v>520</v>
       </c>
@@ -14671,7 +14701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:15" hidden="1">
+    <row r="346" spans="1:15">
       <c r="A346" t="s">
         <v>522</v>
       </c>
@@ -14688,7 +14718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:15" hidden="1">
+    <row r="347" spans="1:15">
       <c r="A347" t="s">
         <v>380</v>
       </c>
@@ -14717,7 +14747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:15" hidden="1">
+    <row r="348" spans="1:15">
       <c r="A348" t="s">
         <v>150</v>
       </c>
@@ -14746,7 +14776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:15" hidden="1">
+    <row r="349" spans="1:15">
       <c r="A349" t="s">
         <v>442</v>
       </c>
@@ -14775,7 +14805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:15" hidden="1">
+    <row r="350" spans="1:15">
       <c r="A350" t="s">
         <v>527</v>
       </c>
@@ -14804,7 +14834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:15" hidden="1">
+    <row r="351" spans="1:15">
       <c r="A351" t="s">
         <v>89</v>
       </c>
@@ -14833,7 +14863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:15" hidden="1">
+    <row r="352" spans="1:15">
       <c r="A352" t="s">
         <v>530</v>
       </c>
@@ -14862,7 +14892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:15" hidden="1">
+    <row r="353" spans="1:15">
       <c r="A353" t="s">
         <v>69</v>
       </c>
@@ -14891,7 +14921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:15" hidden="1">
+    <row r="354" spans="1:15">
       <c r="A354" t="s">
         <v>533</v>
       </c>
@@ -14967,7 +14997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:15" hidden="1">
+    <row r="356" spans="1:15">
       <c r="A356" t="s">
         <v>350</v>
       </c>
@@ -14996,7 +15026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:15" hidden="1">
+    <row r="357" spans="1:15">
       <c r="A357" t="s">
         <v>350</v>
       </c>
@@ -15025,7 +15055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:15" hidden="1">
+    <row r="358" spans="1:15">
       <c r="A358" t="s">
         <v>538</v>
       </c>
@@ -15054,7 +15084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:15" hidden="1">
+    <row r="359" spans="1:15">
       <c r="A359" t="s">
         <v>382</v>
       </c>
@@ -15071,7 +15101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:15" hidden="1">
+    <row r="360" spans="1:15">
       <c r="A360" t="s">
         <v>430</v>
       </c>
@@ -15088,7 +15118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:15" hidden="1">
+    <row r="361" spans="1:15">
       <c r="A361" t="s">
         <v>541</v>
       </c>
@@ -15105,7 +15135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:15" s="6" customFormat="1" hidden="1">
+    <row r="362" spans="1:15" s="6" customFormat="1">
       <c r="A362" s="6" t="s">
         <v>432</v>
       </c>
@@ -15126,7 +15156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:15" hidden="1">
+    <row r="363" spans="1:15">
       <c r="A363" t="s">
         <v>543</v>
       </c>
@@ -15143,7 +15173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:15" hidden="1">
+    <row r="364" spans="1:15">
       <c r="A364" t="s">
         <v>358</v>
       </c>
@@ -15219,7 +15249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:15" hidden="1">
+    <row r="366" spans="1:15">
       <c r="A366" t="s">
         <v>380</v>
       </c>
@@ -15251,7 +15281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:15" hidden="1">
+    <row r="367" spans="1:15">
       <c r="A367" t="s">
         <v>69</v>
       </c>
@@ -15283,7 +15313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:15" hidden="1">
+    <row r="368" spans="1:15">
       <c r="A368" t="s">
         <v>247</v>
       </c>
@@ -15315,7 +15345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:15" hidden="1">
+    <row r="369" spans="1:15">
       <c r="A369" t="s">
         <v>420</v>
       </c>
@@ -15344,54 +15374,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:15" s="11" customFormat="1">
-      <c r="A370" s="11" t="s">
+    <row r="370" spans="1:15">
+      <c r="A370" t="s">
         <v>297</v>
       </c>
-      <c r="B370" s="11" t="s">
+      <c r="B370" t="s">
         <v>551</v>
       </c>
-      <c r="C370" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D370" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E370" s="12">
+      <c r="C370" t="s">
+        <v>17</v>
+      </c>
+      <c r="D370" t="s">
+        <v>35</v>
+      </c>
+      <c r="E370" s="1">
         <v>45873</v>
       </c>
-      <c r="F370" s="11" t="s">
+      <c r="F370" t="s">
         <v>5</v>
       </c>
-      <c r="G370" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H370" s="11" t="s">
+      <c r="G370" t="s">
+        <v>20</v>
+      </c>
+      <c r="H370" t="s">
         <v>458</v>
       </c>
-      <c r="I370" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J370" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K370" s="11" t="s">
+      <c r="I370" t="s">
+        <v>20</v>
+      </c>
+      <c r="J370" t="s">
+        <v>20</v>
+      </c>
+      <c r="K370" t="s">
         <v>31</v>
       </c>
-      <c r="L370" s="11" t="s">
+      <c r="L370" t="s">
         <v>31</v>
       </c>
-      <c r="M370" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="N370" s="11">
+      <c r="M370" t="s">
+        <v>20</v>
+      </c>
+      <c r="N370">
         <v>2015</v>
       </c>
-      <c r="O370" s="13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="371" spans="1:15" hidden="1">
+      <c r="O370" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:15">
       <c r="A371" t="s">
         <v>530</v>
       </c>
@@ -15420,7 +15450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:15" hidden="1">
+    <row r="372" spans="1:15">
       <c r="A372" t="s">
         <v>553</v>
       </c>
@@ -15449,7 +15479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:15" hidden="1">
+    <row r="373" spans="1:15">
       <c r="A373" t="s">
         <v>86</v>
       </c>
@@ -15572,7 +15602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:15" hidden="1">
+    <row r="376" spans="1:15">
       <c r="A376" t="s">
         <v>160</v>
       </c>
@@ -15601,7 +15631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:15" hidden="1">
+    <row r="377" spans="1:15">
       <c r="A377" t="s">
         <v>527</v>
       </c>
@@ -15630,7 +15660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:15" hidden="1">
+    <row r="378" spans="1:15">
       <c r="A378" t="s">
         <v>561</v>
       </c>
@@ -15659,7 +15689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:15" hidden="1">
+    <row r="379" spans="1:15">
       <c r="A379" t="s">
         <v>563</v>
       </c>
@@ -15688,7 +15718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:15" hidden="1">
+    <row r="380" spans="1:15">
       <c r="A380" t="s">
         <v>196</v>
       </c>
@@ -15717,7 +15747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:15" hidden="1">
+    <row r="381" spans="1:15">
       <c r="A381" t="s">
         <v>505</v>
       </c>
@@ -15746,7 +15776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:15" hidden="1">
+    <row r="382" spans="1:15">
       <c r="A382" t="s">
         <v>567</v>
       </c>
@@ -15775,7 +15805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:15" hidden="1">
+    <row r="383" spans="1:15">
       <c r="A383" t="s">
         <v>569</v>
       </c>
@@ -15804,7 +15834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:15" hidden="1">
+    <row r="384" spans="1:15">
       <c r="A384" t="s">
         <v>570</v>
       </c>
@@ -15833,7 +15863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:15" hidden="1">
+    <row r="385" spans="1:15">
       <c r="A385" t="s">
         <v>231</v>
       </c>
@@ -15862,7 +15892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:15" hidden="1">
+    <row r="386" spans="1:15">
       <c r="A386" t="s">
         <v>105</v>
       </c>
@@ -15891,7 +15921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:15" hidden="1">
+    <row r="387" spans="1:15">
       <c r="A387" t="s">
         <v>572</v>
       </c>
@@ -15908,7 +15938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:15" hidden="1">
+    <row r="388" spans="1:15">
       <c r="A388" t="s">
         <v>399</v>
       </c>
@@ -15937,7 +15967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:15" hidden="1">
+    <row r="389" spans="1:15">
       <c r="A389" t="s">
         <v>163</v>
       </c>
@@ -15966,7 +15996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:15" hidden="1">
+    <row r="390" spans="1:15">
       <c r="A390" t="s">
         <v>198</v>
       </c>
@@ -15995,7 +16025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:15" hidden="1">
+    <row r="391" spans="1:15">
       <c r="A391" t="s">
         <v>530</v>
       </c>
@@ -16024,7 +16054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:15" hidden="1">
+    <row r="392" spans="1:15">
       <c r="A392" t="s">
         <v>69</v>
       </c>
@@ -16053,7 +16083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:15" hidden="1">
+    <row r="393" spans="1:15">
       <c r="A393" t="s">
         <v>231</v>
       </c>
@@ -16082,7 +16112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:15" hidden="1">
+    <row r="394" spans="1:15">
       <c r="A394" t="s">
         <v>362</v>
       </c>
@@ -16099,7 +16129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:15" hidden="1">
+    <row r="395" spans="1:15">
       <c r="A395" t="s">
         <v>376</v>
       </c>
@@ -16116,7 +16146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:15" hidden="1">
+    <row r="396" spans="1:15">
       <c r="A396" t="s">
         <v>581</v>
       </c>
@@ -16133,7 +16163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397" spans="1:15" hidden="1">
+    <row r="397" spans="1:15">
       <c r="A397" t="s">
         <v>567</v>
       </c>
@@ -16150,7 +16180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:15" hidden="1">
+    <row r="398" spans="1:15">
       <c r="A398" t="s">
         <v>569</v>
       </c>
@@ -16167,7 +16197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:15" hidden="1">
+    <row r="399" spans="1:15">
       <c r="A399" t="s">
         <v>570</v>
       </c>
@@ -16184,7 +16214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="400" spans="1:15" hidden="1">
+    <row r="400" spans="1:15">
       <c r="A400" t="s">
         <v>208</v>
       </c>
@@ -16201,7 +16231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="1:15" hidden="1">
+    <row r="401" spans="1:15">
       <c r="A401" t="s">
         <v>136</v>
       </c>
@@ -16230,7 +16260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:15" hidden="1">
+    <row r="402" spans="1:15">
       <c r="A402" t="s">
         <v>430</v>
       </c>
@@ -16259,7 +16289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:15" s="6" customFormat="1" hidden="1">
+    <row r="403" spans="1:15" s="6" customFormat="1">
       <c r="A403" s="6" t="s">
         <v>432</v>
       </c>
@@ -16324,7 +16354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:15" hidden="1">
+    <row r="405" spans="1:15">
       <c r="A405" t="s">
         <v>146</v>
       </c>
@@ -16353,7 +16383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:15" hidden="1">
+    <row r="406" spans="1:15">
       <c r="A406" t="s">
         <v>588</v>
       </c>
@@ -16382,7 +16412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:15" hidden="1">
+    <row r="407" spans="1:15">
       <c r="A407" t="s">
         <v>160</v>
       </c>
@@ -16411,7 +16441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:15" hidden="1">
+    <row r="408" spans="1:15">
       <c r="A408" t="s">
         <v>591</v>
       </c>
@@ -16440,7 +16470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:15" hidden="1">
+    <row r="409" spans="1:15">
       <c r="A409" t="s">
         <v>593</v>
       </c>
@@ -16457,7 +16487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:15" hidden="1">
+    <row r="410" spans="1:15">
       <c r="A410" t="s">
         <v>477</v>
       </c>
@@ -16486,7 +16516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:15" hidden="1">
+    <row r="411" spans="1:15">
       <c r="A411" t="s">
         <v>75</v>
       </c>
@@ -16515,7 +16545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:15" hidden="1">
+    <row r="412" spans="1:15">
       <c r="A412" t="s">
         <v>597</v>
       </c>
@@ -16544,7 +16574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:15" hidden="1">
+    <row r="413" spans="1:15">
       <c r="A413" t="s">
         <v>396</v>
       </c>
@@ -16573,7 +16603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:15" hidden="1">
+    <row r="414" spans="1:15">
       <c r="A414" t="s">
         <v>69</v>
       </c>
@@ -16602,7 +16632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:15" hidden="1">
+    <row r="415" spans="1:15">
       <c r="A415" t="s">
         <v>69</v>
       </c>
@@ -16631,7 +16661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:15" hidden="1">
+    <row r="416" spans="1:15">
       <c r="A416" t="s">
         <v>442</v>
       </c>
@@ -16660,7 +16690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:15" hidden="1">
+    <row r="417" spans="1:15">
       <c r="A417" t="s">
         <v>158</v>
       </c>
@@ -16689,7 +16719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:15" hidden="1">
+    <row r="418" spans="1:15">
       <c r="A418" t="s">
         <v>125</v>
       </c>
@@ -16718,7 +16748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:15" hidden="1">
+    <row r="419" spans="1:15">
       <c r="A419" t="s">
         <v>69</v>
       </c>
@@ -16747,7 +16777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:15" hidden="1">
+    <row r="420" spans="1:15">
       <c r="A420" t="s">
         <v>360</v>
       </c>
@@ -16823,7 +16853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:15" hidden="1">
+    <row r="422" spans="1:15">
       <c r="A422" t="s">
         <v>543</v>
       </c>
@@ -16899,7 +16929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:15" hidden="1">
+    <row r="424" spans="1:15">
       <c r="A424" t="s">
         <v>440</v>
       </c>
@@ -16928,7 +16958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:15" hidden="1">
+    <row r="425" spans="1:15">
       <c r="A425" t="s">
         <v>610</v>
       </c>
@@ -16957,7 +16987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:15" hidden="1">
+    <row r="426" spans="1:15">
       <c r="A426" t="s">
         <v>477</v>
       </c>
@@ -17033,7 +17063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:15" hidden="1">
+    <row r="428" spans="1:15">
       <c r="A428" t="s">
         <v>160</v>
       </c>
@@ -17062,7 +17092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:15" hidden="1">
+    <row r="429" spans="1:15">
       <c r="A429" t="s">
         <v>430</v>
       </c>
@@ -17091,7 +17121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:15" s="6" customFormat="1" hidden="1">
+    <row r="430" spans="1:15" s="6" customFormat="1">
       <c r="A430" s="6" t="s">
         <v>432</v>
       </c>
@@ -17206,7 +17236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:15" hidden="1">
+    <row r="433" spans="1:15">
       <c r="A433" t="s">
         <v>260</v>
       </c>
@@ -17223,7 +17253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:15" hidden="1">
+    <row r="434" spans="1:15">
       <c r="A434" t="s">
         <v>262</v>
       </c>
@@ -17240,7 +17270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:15" hidden="1">
+    <row r="435" spans="1:15">
       <c r="A435" t="s">
         <v>109</v>
       </c>
@@ -17316,7 +17346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:15" hidden="1">
+    <row r="437" spans="1:15">
       <c r="A437" t="s">
         <v>221</v>
       </c>
@@ -17333,7 +17363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="438" spans="1:15" hidden="1">
+    <row r="438" spans="1:15">
       <c r="A438" t="s">
         <v>622</v>
       </c>
@@ -17350,7 +17380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="439" spans="1:15" hidden="1">
+    <row r="439" spans="1:15">
       <c r="A439" t="s">
         <v>95</v>
       </c>
@@ -17379,7 +17409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:15" hidden="1">
+    <row r="440" spans="1:15">
       <c r="A440" t="s">
         <v>624</v>
       </c>
@@ -17396,7 +17426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="441" spans="1:15" hidden="1">
+    <row r="441" spans="1:15">
       <c r="A441" t="s">
         <v>626</v>
       </c>
@@ -17425,7 +17455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:15" hidden="1">
+    <row r="442" spans="1:15">
       <c r="A442" t="s">
         <v>628</v>
       </c>
@@ -17454,7 +17484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:15" hidden="1">
+    <row r="443" spans="1:15">
       <c r="A443" t="s">
         <v>430</v>
       </c>
@@ -17483,7 +17513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:15" s="6" customFormat="1" hidden="1">
+    <row r="444" spans="1:15" s="6" customFormat="1">
       <c r="A444" s="6" t="s">
         <v>432</v>
       </c>
@@ -17504,7 +17534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:15" hidden="1">
+    <row r="445" spans="1:15">
       <c r="A445" t="s">
         <v>591</v>
       </c>
@@ -17533,7 +17563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:15" hidden="1">
+    <row r="446" spans="1:15">
       <c r="A446" t="s">
         <v>527</v>
       </c>
@@ -17562,7 +17592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:15" hidden="1">
+    <row r="447" spans="1:15">
       <c r="A447" t="s">
         <v>527</v>
       </c>
@@ -17591,7 +17621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:15" hidden="1">
+    <row r="448" spans="1:15">
       <c r="A448" t="s">
         <v>243</v>
       </c>
@@ -17620,7 +17650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:15" hidden="1">
+    <row r="449" spans="1:15">
       <c r="A449" t="s">
         <v>286</v>
       </c>
@@ -17649,7 +17679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:15" hidden="1">
+    <row r="450" spans="1:15">
       <c r="A450" t="s">
         <v>196</v>
       </c>
@@ -17819,7 +17849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:15" hidden="1">
+    <row r="454" spans="1:15">
       <c r="A454" t="s">
         <v>643</v>
       </c>
@@ -17848,7 +17878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:15" hidden="1">
+    <row r="455" spans="1:15">
       <c r="A455" t="s">
         <v>360</v>
       </c>
@@ -17877,7 +17907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:15" hidden="1">
+    <row r="456" spans="1:15">
       <c r="A456" t="s">
         <v>645</v>
       </c>
@@ -17906,7 +17936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:15" hidden="1">
+    <row r="457" spans="1:15">
       <c r="A457" t="s">
         <v>125</v>
       </c>
@@ -17935,7 +17965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:15" hidden="1">
+    <row r="458" spans="1:15">
       <c r="A458" t="s">
         <v>533</v>
       </c>
@@ -18011,7 +18041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:15" hidden="1">
+    <row r="460" spans="1:15">
       <c r="A460" t="s">
         <v>647</v>
       </c>
@@ -18040,7 +18070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:15" hidden="1">
+    <row r="461" spans="1:15">
       <c r="A461" t="s">
         <v>647</v>
       </c>
@@ -18069,7 +18099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:15" hidden="1">
+    <row r="462" spans="1:15">
       <c r="A462" t="s">
         <v>650</v>
       </c>
@@ -18098,7 +18128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:15" hidden="1">
+    <row r="463" spans="1:15">
       <c r="A463" t="s">
         <v>652</v>
       </c>
@@ -18127,7 +18157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:15" hidden="1">
+    <row r="464" spans="1:15">
       <c r="A464" t="s">
         <v>591</v>
       </c>
@@ -18144,7 +18174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="465" spans="1:15" hidden="1">
+    <row r="465" spans="1:15">
       <c r="A465" t="s">
         <v>654</v>
       </c>
@@ -18173,7 +18203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:15" hidden="1">
+    <row r="466" spans="1:15">
       <c r="A466" t="s">
         <v>656</v>
       </c>
@@ -18202,7 +18232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:15" hidden="1">
+    <row r="467" spans="1:15">
       <c r="A467" t="s">
         <v>426</v>
       </c>
@@ -18231,7 +18261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:15" hidden="1">
+    <row r="468" spans="1:15">
       <c r="A468" t="s">
         <v>659</v>
       </c>
@@ -18248,7 +18278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="469" spans="1:15" hidden="1">
+    <row r="469" spans="1:15">
       <c r="A469" t="s">
         <v>69</v>
       </c>
@@ -18277,7 +18307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:15" hidden="1">
+    <row r="470" spans="1:15">
       <c r="A470" t="s">
         <v>125</v>
       </c>
@@ -18306,7 +18336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:15" hidden="1">
+    <row r="471" spans="1:15">
       <c r="A471" t="s">
         <v>663</v>
       </c>
@@ -18335,7 +18365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:15" hidden="1">
+    <row r="472" spans="1:15">
       <c r="A472" t="s">
         <v>118</v>
       </c>
@@ -18352,7 +18382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="473" spans="1:15" hidden="1">
+    <row r="473" spans="1:15">
       <c r="A473" t="s">
         <v>193</v>
       </c>
@@ -18381,7 +18411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:15" hidden="1">
+    <row r="474" spans="1:15">
       <c r="A474" t="s">
         <v>667</v>
       </c>
@@ -18398,7 +18428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="475" spans="1:15" hidden="1">
+    <row r="475" spans="1:15">
       <c r="A475" t="s">
         <v>669</v>
       </c>
@@ -18427,7 +18457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:15" hidden="1">
+    <row r="476" spans="1:15">
       <c r="A476" t="s">
         <v>671</v>
       </c>
@@ -18444,7 +18474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="477" spans="1:15" hidden="1">
+    <row r="477" spans="1:15">
       <c r="A477" t="s">
         <v>358</v>
       </c>
@@ -18461,7 +18491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="478" spans="1:15" hidden="1">
+    <row r="478" spans="1:15">
       <c r="A478" t="s">
         <v>610</v>
       </c>
@@ -18478,7 +18508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:15" hidden="1">
+    <row r="479" spans="1:15">
       <c r="A479" t="s">
         <v>673</v>
       </c>
@@ -18495,7 +18525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="480" spans="1:15" hidden="1">
+    <row r="480" spans="1:15">
       <c r="A480" t="s">
         <v>675</v>
       </c>
@@ -18524,7 +18554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:15" hidden="1">
+    <row r="481" spans="1:15">
       <c r="A481" t="s">
         <v>217</v>
       </c>
@@ -18600,7 +18630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:15" hidden="1">
+    <row r="483" spans="1:15">
       <c r="A483" t="s">
         <v>103</v>
       </c>
@@ -18629,7 +18659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:15" hidden="1">
+    <row r="484" spans="1:15">
       <c r="A484" t="s">
         <v>533</v>
       </c>
@@ -18658,7 +18688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:15" hidden="1">
+    <row r="485" spans="1:15">
       <c r="A485" t="s">
         <v>136</v>
       </c>
@@ -18734,7 +18764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:15" hidden="1">
+    <row r="487" spans="1:15">
       <c r="A487" t="s">
         <v>683</v>
       </c>
@@ -18763,7 +18793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:15" hidden="1">
+    <row r="488" spans="1:15">
       <c r="A488" t="s">
         <v>685</v>
       </c>
@@ -18839,7 +18869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:15" hidden="1">
+    <row r="490" spans="1:15">
       <c r="A490" t="s">
         <v>689</v>
       </c>
@@ -18868,7 +18898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:15" hidden="1">
+    <row r="491" spans="1:15">
       <c r="A491" t="s">
         <v>691</v>
       </c>
@@ -18897,7 +18927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:15" hidden="1">
+    <row r="492" spans="1:15">
       <c r="A492" t="s">
         <v>691</v>
       </c>
@@ -18926,7 +18956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:15" hidden="1">
+    <row r="493" spans="1:15">
       <c r="A493" t="s">
         <v>694</v>
       </c>
@@ -18955,7 +18985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:15" hidden="1">
+    <row r="494" spans="1:15">
       <c r="A494" t="s">
         <v>691</v>
       </c>
@@ -18984,7 +19014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:15" hidden="1">
+    <row r="495" spans="1:15">
       <c r="A495" t="s">
         <v>697</v>
       </c>
@@ -19013,7 +19043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:15" hidden="1">
+    <row r="496" spans="1:15">
       <c r="A496" t="s">
         <v>697</v>
       </c>
@@ -19042,7 +19072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:15" hidden="1">
+    <row r="497" spans="1:15">
       <c r="A497" t="s">
         <v>697</v>
       </c>
@@ -19071,7 +19101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:15" hidden="1">
+    <row r="498" spans="1:15">
       <c r="A498" t="s">
         <v>697</v>
       </c>
@@ -19100,7 +19130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:15" hidden="1">
+    <row r="499" spans="1:15">
       <c r="A499" t="s">
         <v>702</v>
       </c>
@@ -19176,7 +19206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:15" hidden="1">
+    <row r="501" spans="1:15">
       <c r="A501" t="s">
         <v>706</v>
       </c>
@@ -19205,7 +19235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:15" hidden="1">
+    <row r="502" spans="1:15">
       <c r="A502" t="s">
         <v>708</v>
       </c>
@@ -19375,7 +19405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:15" hidden="1">
+    <row r="506" spans="1:15">
       <c r="A506" t="s">
         <v>691</v>
       </c>
@@ -19451,7 +19481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:15" hidden="1">
+    <row r="508" spans="1:15">
       <c r="A508" t="s">
         <v>691</v>
       </c>
@@ -19480,7 +19510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="509" spans="1:15" hidden="1">
+    <row r="509" spans="1:15">
       <c r="A509" t="s">
         <v>685</v>
       </c>
@@ -19509,7 +19539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:15" hidden="1">
+    <row r="510" spans="1:15">
       <c r="A510" t="s">
         <v>89</v>
       </c>
@@ -19538,7 +19568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:15" s="6" customFormat="1" hidden="1">
+    <row r="511" spans="1:15" s="6" customFormat="1">
       <c r="A511" s="6" t="s">
         <v>721</v>
       </c>
@@ -19561,7 +19591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:15" hidden="1">
+    <row r="512" spans="1:15">
       <c r="A512" t="s">
         <v>721</v>
       </c>
@@ -19578,7 +19608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="513" spans="1:16" hidden="1">
+    <row r="513" spans="1:16">
       <c r="A513" t="s">
         <v>683</v>
       </c>
@@ -19607,7 +19637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:16" hidden="1">
+    <row r="514" spans="1:16">
       <c r="A514" t="s">
         <v>706</v>
       </c>
@@ -19683,7 +19713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:16" hidden="1">
+    <row r="516" spans="1:16">
       <c r="A516" t="s">
         <v>728</v>
       </c>
@@ -19712,7 +19742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:16" hidden="1">
+    <row r="517" spans="1:16">
       <c r="A517" t="s">
         <v>704</v>
       </c>
@@ -19741,7 +19771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:16" hidden="1">
+    <row r="518" spans="1:16">
       <c r="A518" t="s">
         <v>731</v>
       </c>
@@ -19770,7 +19800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:16" hidden="1">
+    <row r="519" spans="1:16">
       <c r="A519" t="s">
         <v>733</v>
       </c>
@@ -19834,7 +19864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:16" hidden="1">
+    <row r="521" spans="1:16">
       <c r="A521" t="s">
         <v>737</v>
       </c>
@@ -19863,7 +19893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:16" hidden="1">
+    <row r="522" spans="1:16">
       <c r="A522" t="s">
         <v>370</v>
       </c>
@@ -19892,7 +19922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:16" hidden="1">
+    <row r="523" spans="1:16">
       <c r="A523" t="s">
         <v>740</v>
       </c>
@@ -19921,7 +19951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:16" hidden="1">
+    <row r="524" spans="1:16">
       <c r="A524" t="s">
         <v>742</v>
       </c>
@@ -19950,7 +19980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:16" hidden="1">
+    <row r="525" spans="1:16">
       <c r="A525" t="s">
         <v>744</v>
       </c>
@@ -19979,7 +20009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:16" hidden="1">
+    <row r="526" spans="1:16">
       <c r="A526" t="s">
         <v>689</v>
       </c>
@@ -20008,7 +20038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527" spans="1:16" hidden="1">
+    <row r="527" spans="1:16">
       <c r="A527" t="s">
         <v>89</v>
       </c>
@@ -20134,7 +20164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:16" hidden="1">
+    <row r="530" spans="1:16">
       <c r="A530" t="s">
         <v>754</v>
       </c>
@@ -20163,7 +20193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:16" hidden="1">
+    <row r="531" spans="1:16">
       <c r="A531" t="s">
         <v>563</v>
       </c>
@@ -20192,7 +20222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:16" hidden="1">
+    <row r="532" spans="1:16">
       <c r="A532" t="s">
         <v>563</v>
       </c>
@@ -20221,7 +20251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:16" hidden="1">
+    <row r="533" spans="1:16">
       <c r="A533" t="s">
         <v>563</v>
       </c>
@@ -20250,7 +20280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:16" hidden="1">
+    <row r="534" spans="1:16">
       <c r="A534" t="s">
         <v>563</v>
       </c>
@@ -20279,7 +20309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:16" hidden="1">
+    <row r="535" spans="1:16">
       <c r="A535" t="s">
         <v>563</v>
       </c>
@@ -20308,7 +20338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:16" hidden="1">
+    <row r="536" spans="1:16">
       <c r="A536" t="s">
         <v>563</v>
       </c>
@@ -20387,7 +20417,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="538" spans="1:16" hidden="1">
+    <row r="538" spans="1:16">
       <c r="A538" t="s">
         <v>563</v>
       </c>
@@ -20416,7 +20446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:16" hidden="1">
+    <row r="539" spans="1:16">
       <c r="A539" t="s">
         <v>563</v>
       </c>
@@ -20445,7 +20475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:16" hidden="1">
+    <row r="540" spans="1:16">
       <c r="A540" t="s">
         <v>769</v>
       </c>
@@ -20474,7 +20504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:16" hidden="1">
+    <row r="541" spans="1:16">
       <c r="A541" t="s">
         <v>563</v>
       </c>
@@ -20503,7 +20533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:16" hidden="1">
+    <row r="542" spans="1:16">
       <c r="A542" t="s">
         <v>563</v>
       </c>
@@ -20532,7 +20562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:16" hidden="1">
+    <row r="543" spans="1:16">
       <c r="A543" t="s">
         <v>563</v>
       </c>
@@ -20561,7 +20591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:16" hidden="1">
+    <row r="544" spans="1:16">
       <c r="A544" t="s">
         <v>543</v>
       </c>
@@ -20590,7 +20620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:15" hidden="1">
+    <row r="545" spans="1:15">
       <c r="A545" t="s">
         <v>563</v>
       </c>
@@ -20619,7 +20649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:15" hidden="1">
+    <row r="546" spans="1:15">
       <c r="A546" t="s">
         <v>563</v>
       </c>
@@ -20742,7 +20772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:15" hidden="1">
+    <row r="549" spans="1:15">
       <c r="A549" t="s">
         <v>563</v>
       </c>
@@ -20771,7 +20801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550" spans="1:15" hidden="1">
+    <row r="550" spans="1:15">
       <c r="A550" t="s">
         <v>781</v>
       </c>
@@ -20800,7 +20830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551" spans="1:15" hidden="1">
+    <row r="551" spans="1:15">
       <c r="A551" t="s">
         <v>563</v>
       </c>
@@ -20829,7 +20859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:15" hidden="1">
+    <row r="552" spans="1:15">
       <c r="A552" t="s">
         <v>563</v>
       </c>
@@ -20858,7 +20888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:15" hidden="1">
+    <row r="553" spans="1:15">
       <c r="A553" t="s">
         <v>543</v>
       </c>
@@ -20887,7 +20917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:15" hidden="1">
+    <row r="554" spans="1:15">
       <c r="A554" t="s">
         <v>563</v>
       </c>
@@ -20916,7 +20946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:15" hidden="1">
+    <row r="555" spans="1:15">
       <c r="A555" t="s">
         <v>563</v>
       </c>
@@ -20945,7 +20975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="556" spans="1:15" hidden="1">
+    <row r="556" spans="1:15">
       <c r="A556" t="s">
         <v>563</v>
       </c>
@@ -21021,7 +21051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:15" hidden="1">
+    <row r="558" spans="1:15">
       <c r="A558" t="s">
         <v>790</v>
       </c>
@@ -21050,7 +21080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:15" hidden="1">
+    <row r="559" spans="1:15">
       <c r="A559" t="s">
         <v>563</v>
       </c>
@@ -21079,48 +21109,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560" spans="1:15" s="6" customFormat="1">
-      <c r="A560" s="6" t="s">
+    <row r="560" spans="1:15">
+      <c r="A560" t="s">
         <v>777</v>
       </c>
-      <c r="B560" s="6" t="s">
+      <c r="B560" t="s">
         <v>793</v>
       </c>
-      <c r="C560" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D560" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E560" s="8">
+      <c r="C560" t="s">
+        <v>17</v>
+      </c>
+      <c r="D560" t="s">
+        <v>35</v>
+      </c>
+      <c r="E560" s="1">
         <v>45874</v>
       </c>
-      <c r="F560" s="6" t="s">
+      <c r="F560" t="s">
         <v>5</v>
       </c>
-      <c r="G560" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H560" s="6" t="s">
+      <c r="G560" t="s">
+        <v>20</v>
+      </c>
+      <c r="H560" t="s">
         <v>756</v>
       </c>
-      <c r="I560" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J560" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K560" s="6" t="s">
+      <c r="I560" t="s">
+        <v>20</v>
+      </c>
+      <c r="J560" t="s">
+        <v>20</v>
+      </c>
+      <c r="K560" t="s">
         <v>31</v>
       </c>
-      <c r="L560" s="6" t="s">
+      <c r="L560" t="s">
         <v>764</v>
       </c>
-      <c r="O560" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="561" spans="1:15" hidden="1">
+      <c r="M560" t="s">
+        <v>765</v>
+      </c>
+      <c r="N560">
+        <v>2019</v>
+      </c>
+      <c r="O560" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="1:15">
       <c r="A561" t="s">
         <v>563</v>
       </c>
@@ -21149,7 +21185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="562" spans="1:15" hidden="1">
+    <row r="562" spans="1:15">
       <c r="A562" t="s">
         <v>563</v>
       </c>
@@ -21178,7 +21214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="563" spans="1:15" hidden="1">
+    <row r="563" spans="1:15">
       <c r="A563" t="s">
         <v>563</v>
       </c>
@@ -21207,7 +21243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:15" hidden="1">
+    <row r="564" spans="1:15">
       <c r="A564" t="s">
         <v>563</v>
       </c>
@@ -21236,7 +21272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:15" hidden="1">
+    <row r="565" spans="1:15">
       <c r="A565" t="s">
         <v>798</v>
       </c>
@@ -21265,7 +21301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="566" spans="1:15" hidden="1">
+    <row r="566" spans="1:15">
       <c r="A566" t="s">
         <v>800</v>
       </c>
@@ -21294,7 +21330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:15" hidden="1">
+    <row r="567" spans="1:15">
       <c r="A567" t="s">
         <v>202</v>
       </c>
@@ -21323,7 +21359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:15" hidden="1">
+    <row r="568" spans="1:15">
       <c r="A568" t="s">
         <v>563</v>
       </c>
@@ -21352,7 +21388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:15" hidden="1">
+    <row r="569" spans="1:15">
       <c r="A569" t="s">
         <v>563</v>
       </c>
@@ -21381,48 +21417,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:15" s="6" customFormat="1">
-      <c r="A570" s="6" t="s">
+    <row r="570" spans="1:15">
+      <c r="A570" t="s">
         <v>803</v>
       </c>
-      <c r="B570" s="6" t="s">
+      <c r="B570" t="s">
         <v>804</v>
       </c>
-      <c r="C570" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D570" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E570" s="8">
+      <c r="C570" t="s">
+        <v>17</v>
+      </c>
+      <c r="D570" t="s">
+        <v>35</v>
+      </c>
+      <c r="E570" s="1">
         <v>45888</v>
       </c>
-      <c r="F570" s="6" t="s">
+      <c r="F570" t="s">
         <v>5</v>
       </c>
-      <c r="G570" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H570" s="6" t="s">
+      <c r="G570" t="s">
+        <v>20</v>
+      </c>
+      <c r="H570" t="s">
         <v>756</v>
       </c>
-      <c r="I570" s="6" t="s">
+      <c r="I570" t="s">
         <v>212</v>
       </c>
-      <c r="J570" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K570" s="6" t="s">
+      <c r="J570" t="s">
+        <v>20</v>
+      </c>
+      <c r="K570" t="s">
         <v>31</v>
       </c>
-      <c r="L570" s="6" t="s">
+      <c r="L570" t="s">
         <v>805</v>
       </c>
-      <c r="O570" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="571" spans="1:15" hidden="1">
+      <c r="M570" t="s">
+        <v>765</v>
+      </c>
+      <c r="N570">
+        <v>2023</v>
+      </c>
+      <c r="O570" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="1:15">
       <c r="A571" t="s">
         <v>284</v>
       </c>
@@ -21451,7 +21493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:15" hidden="1">
+    <row r="572" spans="1:15">
       <c r="A572" t="s">
         <v>563</v>
       </c>
@@ -21480,7 +21522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:15" hidden="1">
+    <row r="573" spans="1:15">
       <c r="A573" t="s">
         <v>563</v>
       </c>
@@ -21509,7 +21551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:15" hidden="1">
+    <row r="574" spans="1:15">
       <c r="A574" t="s">
         <v>563</v>
       </c>
@@ -21538,7 +21580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:15" hidden="1">
+    <row r="575" spans="1:15">
       <c r="A575" t="s">
         <v>563</v>
       </c>
@@ -21567,7 +21609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:15" hidden="1">
+    <row r="576" spans="1:15">
       <c r="A576" t="s">
         <v>563</v>
       </c>
@@ -21596,7 +21638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:15" hidden="1">
+    <row r="577" spans="1:15">
       <c r="A577" t="s">
         <v>563</v>
       </c>
@@ -21625,7 +21667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="578" spans="1:15" hidden="1">
+    <row r="578" spans="1:15">
       <c r="A578" t="s">
         <v>563</v>
       </c>
@@ -21654,7 +21696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579" spans="1:15" hidden="1">
+    <row r="579" spans="1:15">
       <c r="A579" t="s">
         <v>563</v>
       </c>
@@ -21683,7 +21725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:15" hidden="1">
+    <row r="580" spans="1:15">
       <c r="A580" t="s">
         <v>563</v>
       </c>
@@ -21712,7 +21754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:15" hidden="1">
+    <row r="581" spans="1:15">
       <c r="A581" t="s">
         <v>563</v>
       </c>
@@ -21835,7 +21877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:15" hidden="1">
+    <row r="584" spans="1:15">
       <c r="A584" t="s">
         <v>819</v>
       </c>
@@ -21864,7 +21906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:15" hidden="1">
+    <row r="585" spans="1:15">
       <c r="A585" t="s">
         <v>822</v>
       </c>
@@ -21881,7 +21923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="586" spans="1:15" hidden="1">
+    <row r="586" spans="1:15">
       <c r="A586" t="s">
         <v>824</v>
       </c>
@@ -21910,7 +21952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="587" spans="1:15" hidden="1">
+    <row r="587" spans="1:15">
       <c r="A587" t="s">
         <v>826</v>
       </c>
@@ -21927,7 +21969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="588" spans="1:15" hidden="1">
+    <row r="588" spans="1:15">
       <c r="A588" t="s">
         <v>828</v>
       </c>
@@ -21944,7 +21986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="589" spans="1:15" hidden="1">
+    <row r="589" spans="1:15">
       <c r="A589" t="s">
         <v>830</v>
       </c>
@@ -21961,7 +22003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="590" spans="1:15" hidden="1">
+    <row r="590" spans="1:15">
       <c r="A590" t="s">
         <v>832</v>
       </c>
@@ -21990,7 +22032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:15" hidden="1">
+    <row r="591" spans="1:15">
       <c r="A591" t="s">
         <v>834</v>
       </c>
@@ -22019,7 +22061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:15" hidden="1">
+    <row r="592" spans="1:15">
       <c r="A592" t="s">
         <v>819</v>
       </c>
@@ -22048,7 +22090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:15" hidden="1">
+    <row r="593" spans="1:15">
       <c r="A593" t="s">
         <v>837</v>
       </c>
@@ -22077,7 +22119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:15" hidden="1">
+    <row r="594" spans="1:15">
       <c r="A594" t="s">
         <v>832</v>
       </c>
@@ -22109,7 +22151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:15" hidden="1">
+    <row r="595" spans="1:15">
       <c r="A595" t="s">
         <v>841</v>
       </c>
@@ -22138,7 +22180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="596" spans="1:15" hidden="1">
+    <row r="596" spans="1:15">
       <c r="A596" t="s">
         <v>843</v>
       </c>
@@ -22167,7 +22209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="597" spans="1:15" hidden="1">
+    <row r="597" spans="1:15">
       <c r="A597" t="s">
         <v>430</v>
       </c>
@@ -22196,7 +22238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:15" s="6" customFormat="1" hidden="1">
+    <row r="598" spans="1:15" s="6" customFormat="1">
       <c r="A598" s="6" t="s">
         <v>432</v>
       </c>
@@ -22217,7 +22259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="599" spans="1:15" hidden="1">
+    <row r="599" spans="1:15">
       <c r="A599" t="s">
         <v>837</v>
       </c>
@@ -22246,7 +22288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:15" hidden="1">
+    <row r="600" spans="1:15">
       <c r="A600" t="s">
         <v>645</v>
       </c>
@@ -22275,7 +22317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:15" hidden="1">
+    <row r="601" spans="1:15">
       <c r="A601" t="s">
         <v>847</v>
       </c>
@@ -22304,7 +22346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:15" hidden="1">
+    <row r="602" spans="1:15">
       <c r="A602" t="s">
         <v>645</v>
       </c>
@@ -22333,7 +22375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:15" hidden="1">
+    <row r="603" spans="1:15">
       <c r="A603" t="s">
         <v>543</v>
       </c>
@@ -22362,7 +22404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="604" spans="1:15" hidden="1">
+    <row r="604" spans="1:15">
       <c r="A604" t="s">
         <v>849</v>
       </c>
@@ -22391,36 +22433,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="605" spans="1:15" s="6" customFormat="1" hidden="1">
-      <c r="A605" s="6" t="s">
+    <row r="605" spans="1:15">
+      <c r="A605" t="s">
         <v>408</v>
       </c>
-      <c r="B605" s="6" t="s">
+      <c r="B605" t="s">
         <v>851</v>
       </c>
-      <c r="C605" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D605" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E605" s="8">
+      <c r="C605" t="s">
+        <v>17</v>
+      </c>
+      <c r="D605" t="s">
+        <v>35</v>
+      </c>
+      <c r="E605" s="1">
         <v>45874</v>
       </c>
-      <c r="F605" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G605" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H605" s="6" t="s">
+      <c r="F605" t="s">
+        <v>19</v>
+      </c>
+      <c r="G605" t="s">
+        <v>20</v>
+      </c>
+      <c r="H605" t="s">
         <v>821</v>
       </c>
-      <c r="O605" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="606" spans="1:15" hidden="1">
+      <c r="O605" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606" spans="1:15">
       <c r="A606" t="s">
         <v>354</v>
       </c>
@@ -22449,7 +22491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:15" hidden="1">
+    <row r="607" spans="1:15">
       <c r="A607" t="s">
         <v>853</v>
       </c>
@@ -22478,7 +22520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="608" spans="1:15" hidden="1">
+    <row r="608" spans="1:15">
       <c r="A608" t="s">
         <v>855</v>
       </c>
@@ -22507,7 +22549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="609" spans="1:15" hidden="1">
+    <row r="609" spans="1:15">
       <c r="A609" t="s">
         <v>832</v>
       </c>
@@ -22536,7 +22578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="610" spans="1:15" hidden="1">
+    <row r="610" spans="1:15">
       <c r="A610" t="s">
         <v>858</v>
       </c>
@@ -22565,7 +22607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="611" spans="1:15" hidden="1">
+    <row r="611" spans="1:15">
       <c r="A611" t="s">
         <v>861</v>
       </c>
@@ -22594,7 +22636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:15" hidden="1">
+    <row r="612" spans="1:15">
       <c r="A612" t="s">
         <v>858</v>
       </c>
@@ -22623,7 +22665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="613" spans="1:15" hidden="1">
+    <row r="613" spans="1:15">
       <c r="A613" t="s">
         <v>858</v>
       </c>
@@ -22652,7 +22694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="614" spans="1:15" hidden="1">
+    <row r="614" spans="1:15">
       <c r="A614" t="s">
         <v>861</v>
       </c>
@@ -22669,7 +22711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="615" spans="1:15" hidden="1">
+    <row r="615" spans="1:15">
       <c r="A615" t="s">
         <v>866</v>
       </c>
@@ -22735,6 +22777,9 @@
       <c r="L616" t="s">
         <v>32</v>
       </c>
+      <c r="M616" t="s">
+        <v>20</v>
+      </c>
       <c r="N616">
         <v>2018</v>
       </c>
@@ -22742,7 +22787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="617" spans="1:15" hidden="1">
+    <row r="617" spans="1:15">
       <c r="A617" t="s">
         <v>866</v>
       </c>
@@ -22771,7 +22816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:15" hidden="1">
+    <row r="618" spans="1:15">
       <c r="A618" t="s">
         <v>870</v>
       </c>
@@ -22800,7 +22845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:15" hidden="1">
+    <row r="619" spans="1:15">
       <c r="A619" t="s">
         <v>872</v>
       </c>
@@ -22829,7 +22874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="620" spans="1:15" hidden="1">
+    <row r="620" spans="1:15">
       <c r="A620" t="s">
         <v>874</v>
       </c>
@@ -22858,7 +22903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:15" hidden="1">
+    <row r="621" spans="1:15">
       <c r="A621" t="s">
         <v>866</v>
       </c>
@@ -22924,6 +22969,9 @@
       <c r="L622" t="s">
         <v>32</v>
       </c>
+      <c r="M622" t="s">
+        <v>20</v>
+      </c>
       <c r="N622">
         <v>2020</v>
       </c>
@@ -22931,7 +22979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="623" spans="1:15" hidden="1">
+    <row r="623" spans="1:15">
       <c r="A623" t="s">
         <v>870</v>
       </c>
@@ -22960,7 +23008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="624" spans="1:15" hidden="1">
+    <row r="624" spans="1:15">
       <c r="A624" t="s">
         <v>872</v>
       </c>
@@ -22989,7 +23037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:15" hidden="1">
+    <row r="625" spans="1:15">
       <c r="A625" t="s">
         <v>861</v>
       </c>
@@ -23018,7 +23066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="626" spans="1:15" hidden="1">
+    <row r="626" spans="1:15">
       <c r="A626" t="s">
         <v>883</v>
       </c>
@@ -23047,7 +23095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="627" spans="1:15" hidden="1">
+    <row r="627" spans="1:15">
       <c r="A627" t="s">
         <v>861</v>
       </c>
@@ -23076,7 +23124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="628" spans="1:15" hidden="1">
+    <row r="628" spans="1:15">
       <c r="A628" t="s">
         <v>883</v>
       </c>
@@ -23105,7 +23153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="629" spans="1:15" hidden="1">
+    <row r="629" spans="1:15">
       <c r="A629" t="s">
         <v>886</v>
       </c>
@@ -23134,7 +23182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="630" spans="1:15" hidden="1">
+    <row r="630" spans="1:15">
       <c r="A630" t="s">
         <v>889</v>
       </c>
@@ -23163,7 +23211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="631" spans="1:15" hidden="1">
+    <row r="631" spans="1:15">
       <c r="A631" t="s">
         <v>892</v>
       </c>
@@ -23189,7 +23237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="632" spans="1:15" hidden="1">
+    <row r="632" spans="1:15">
       <c r="A632" t="s">
         <v>894</v>
       </c>
@@ -23215,7 +23263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="633" spans="1:15" hidden="1">
+    <row r="633" spans="1:15">
       <c r="A633" t="s">
         <v>895</v>
       </c>
@@ -23241,7 +23289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="634" spans="1:15" hidden="1">
+    <row r="634" spans="1:15">
       <c r="A634" t="s">
         <v>897</v>
       </c>
@@ -23270,7 +23318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="635" spans="1:15" hidden="1">
+    <row r="635" spans="1:15">
       <c r="A635" t="s">
         <v>832</v>
       </c>
@@ -23296,7 +23344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="636" spans="1:15" hidden="1">
+    <row r="636" spans="1:15">
       <c r="A636" t="s">
         <v>902</v>
       </c>
@@ -23325,7 +23373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="637" spans="1:15" hidden="1">
+    <row r="637" spans="1:15">
       <c r="A637" t="s">
         <v>905</v>
       </c>
@@ -23354,7 +23402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="638" spans="1:15" hidden="1">
+    <row r="638" spans="1:15">
       <c r="A638" t="s">
         <v>111</v>
       </c>
@@ -23383,7 +23431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="639" spans="1:15" hidden="1">
+    <row r="639" spans="1:15">
       <c r="A639" t="s">
         <v>713</v>
       </c>
@@ -23412,7 +23460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="640" spans="1:15" hidden="1">
+    <row r="640" spans="1:15">
       <c r="A640" t="s">
         <v>909</v>
       </c>
@@ -23441,7 +23489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="641" spans="1:15" hidden="1">
+    <row r="641" spans="1:15">
       <c r="A641" t="s">
         <v>911</v>
       </c>
@@ -23470,7 +23518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="642" spans="1:15" hidden="1">
+    <row r="642" spans="1:15">
       <c r="A642" t="s">
         <v>913</v>
       </c>
@@ -23499,7 +23547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="643" spans="1:15" hidden="1">
+    <row r="643" spans="1:15">
       <c r="A643" t="s">
         <v>229</v>
       </c>
@@ -23528,7 +23576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="644" spans="1:15" hidden="1">
+    <row r="644" spans="1:15">
       <c r="A644" t="s">
         <v>915</v>
       </c>
@@ -23557,7 +23605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:15" hidden="1">
+    <row r="645" spans="1:15">
       <c r="A645" t="s">
         <v>902</v>
       </c>
@@ -23586,7 +23634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="646" spans="1:15" hidden="1">
+    <row r="646" spans="1:15">
       <c r="A646" t="s">
         <v>63</v>
       </c>
@@ -23615,7 +23663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="647" spans="1:15" hidden="1">
+    <row r="647" spans="1:15">
       <c r="A647" t="s">
         <v>919</v>
       </c>
@@ -23644,7 +23692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="648" spans="1:15" hidden="1">
+    <row r="648" spans="1:15">
       <c r="A648" t="s">
         <v>922</v>
       </c>
@@ -23673,7 +23721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="649" spans="1:15" hidden="1">
+    <row r="649" spans="1:15">
       <c r="A649" t="s">
         <v>925</v>
       </c>
@@ -23702,7 +23750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="650" spans="1:15" hidden="1">
+    <row r="650" spans="1:15">
       <c r="A650" t="s">
         <v>928</v>
       </c>
@@ -23731,7 +23779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="651" spans="1:15" hidden="1">
+    <row r="651" spans="1:15">
       <c r="A651" t="s">
         <v>925</v>
       </c>
@@ -23760,7 +23808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="652" spans="1:15" hidden="1">
+    <row r="652" spans="1:15">
       <c r="A652" t="s">
         <v>925</v>
       </c>
@@ -23789,7 +23837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="653" spans="1:15" hidden="1">
+    <row r="653" spans="1:15">
       <c r="A653" t="s">
         <v>935</v>
       </c>
@@ -23818,7 +23866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="654" spans="1:15" hidden="1">
+    <row r="654" spans="1:15">
       <c r="A654" t="s">
         <v>935</v>
       </c>
@@ -23847,7 +23895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="655" spans="1:15" hidden="1">
+    <row r="655" spans="1:15">
       <c r="A655" t="s">
         <v>935</v>
       </c>
@@ -23876,7 +23924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="656" spans="1:15" hidden="1">
+    <row r="656" spans="1:15">
       <c r="A656" t="s">
         <v>940</v>
       </c>
@@ -23905,7 +23953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="657" spans="1:15" hidden="1">
+    <row r="657" spans="1:15">
       <c r="A657" t="s">
         <v>935</v>
       </c>
@@ -23934,7 +23982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="658" spans="1:15" hidden="1">
+    <row r="658" spans="1:15">
       <c r="A658" t="s">
         <v>943</v>
       </c>
@@ -23963,7 +24011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="659" spans="1:15" hidden="1">
+    <row r="659" spans="1:15">
       <c r="A659" t="s">
         <v>945</v>
       </c>
@@ -23992,7 +24040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="660" spans="1:15" hidden="1">
+    <row r="660" spans="1:15">
       <c r="A660" t="s">
         <v>946</v>
       </c>
@@ -24021,7 +24069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="661" spans="1:15" hidden="1">
+    <row r="661" spans="1:15">
       <c r="A661" t="s">
         <v>886</v>
       </c>
@@ -24050,7 +24098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="662" spans="1:15" hidden="1">
+    <row r="662" spans="1:15">
       <c r="A662" t="s">
         <v>947</v>
       </c>
@@ -24079,7 +24127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="663" spans="1:15" hidden="1">
+    <row r="663" spans="1:15">
       <c r="A663" t="s">
         <v>948</v>
       </c>
@@ -24108,7 +24156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="664" spans="1:15" hidden="1">
+    <row r="664" spans="1:15">
       <c r="A664" t="s">
         <v>949</v>
       </c>
@@ -24137,7 +24185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="665" spans="1:15" hidden="1">
+    <row r="665" spans="1:15">
       <c r="A665" t="s">
         <v>949</v>
       </c>
@@ -24166,7 +24214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="666" spans="1:15" hidden="1">
+    <row r="666" spans="1:15">
       <c r="A666" t="s">
         <v>953</v>
       </c>
@@ -24195,7 +24243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="667" spans="1:15" hidden="1">
+    <row r="667" spans="1:15">
       <c r="A667" t="s">
         <v>956</v>
       </c>
@@ -24224,7 +24272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="668" spans="1:15" hidden="1">
+    <row r="668" spans="1:15">
       <c r="A668" t="s">
         <v>956</v>
       </c>
@@ -24253,7 +24301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="669" spans="1:15" hidden="1">
+    <row r="669" spans="1:15">
       <c r="A669" t="s">
         <v>959</v>
       </c>
@@ -24282,7 +24330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="670" spans="1:15" hidden="1">
+    <row r="670" spans="1:15">
       <c r="A670" t="s">
         <v>960</v>
       </c>
@@ -24311,7 +24359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="671" spans="1:15" hidden="1">
+    <row r="671" spans="1:15">
       <c r="A671" t="s">
         <v>961</v>
       </c>
@@ -24340,7 +24388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="672" spans="1:15" hidden="1">
+    <row r="672" spans="1:15">
       <c r="A672" t="s">
         <v>925</v>
       </c>
@@ -24369,7 +24417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="673" spans="1:15" hidden="1">
+    <row r="673" spans="1:15">
       <c r="A673" t="s">
         <v>965</v>
       </c>
@@ -24398,7 +24446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="674" spans="1:15" hidden="1">
+    <row r="674" spans="1:15">
       <c r="A674" t="s">
         <v>968</v>
       </c>
@@ -24427,7 +24475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="675" spans="1:15" hidden="1">
+    <row r="675" spans="1:15">
       <c r="A675" t="s">
         <v>971</v>
       </c>
@@ -24456,7 +24504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="676" spans="1:15" hidden="1">
+    <row r="676" spans="1:15">
       <c r="A676" t="s">
         <v>925</v>
       </c>
@@ -24485,7 +24533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="677" spans="1:15" hidden="1">
+    <row r="677" spans="1:15">
       <c r="A677" t="s">
         <v>63</v>
       </c>
@@ -24514,7 +24562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="678" spans="1:15" hidden="1">
+    <row r="678" spans="1:15">
       <c r="A678" t="s">
         <v>978</v>
       </c>
@@ -24543,7 +24591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:15" hidden="1">
+    <row r="679" spans="1:15">
       <c r="A679" t="s">
         <v>981</v>
       </c>
@@ -24572,7 +24620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="680" spans="1:15" hidden="1">
+    <row r="680" spans="1:15">
       <c r="A680" t="s">
         <v>984</v>
       </c>
@@ -24601,7 +24649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681" spans="1:15" hidden="1">
+    <row r="681" spans="1:15">
       <c r="A681" t="s">
         <v>987</v>
       </c>
@@ -24627,7 +24675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="682" spans="1:15" hidden="1">
+    <row r="682" spans="1:15">
       <c r="A682" t="s">
         <v>988</v>
       </c>
@@ -24656,7 +24704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="683" spans="1:15" hidden="1">
+    <row r="683" spans="1:15">
       <c r="A683" t="s">
         <v>991</v>
       </c>
@@ -24685,7 +24733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="684" spans="1:15" hidden="1">
+    <row r="684" spans="1:15">
       <c r="A684" t="s">
         <v>563</v>
       </c>
@@ -24714,7 +24762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="685" spans="1:15" hidden="1">
+    <row r="685" spans="1:15">
       <c r="A685" t="s">
         <v>853</v>
       </c>
@@ -24743,7 +24791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="686" spans="1:15" hidden="1">
+    <row r="686" spans="1:15">
       <c r="A686" t="s">
         <v>310</v>
       </c>
@@ -24772,7 +24820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="687" spans="1:15" hidden="1">
+    <row r="687" spans="1:15">
       <c r="A687" t="s">
         <v>998</v>
       </c>
@@ -24801,7 +24849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="688" spans="1:15" hidden="1">
+    <row r="688" spans="1:15">
       <c r="A688" t="s">
         <v>998</v>
       </c>
@@ -24830,7 +24878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="689" spans="1:15" hidden="1">
+    <row r="689" spans="1:15">
       <c r="A689" t="s">
         <v>310</v>
       </c>
@@ -24859,7 +24907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="690" spans="1:15" hidden="1">
+    <row r="690" spans="1:15">
       <c r="A690" t="s">
         <v>998</v>
       </c>
@@ -24888,7 +24936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="691" spans="1:15" hidden="1">
+    <row r="691" spans="1:15">
       <c r="A691" t="s">
         <v>1003</v>
       </c>
@@ -24917,7 +24965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="692" spans="1:15" hidden="1">
+    <row r="692" spans="1:15">
       <c r="A692" t="s">
         <v>1003</v>
       </c>
@@ -24946,7 +24994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="693" spans="1:15" hidden="1">
+    <row r="693" spans="1:15">
       <c r="A693" t="s">
         <v>234</v>
       </c>
@@ -24975,7 +25023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="694" spans="1:15" hidden="1">
+    <row r="694" spans="1:15">
       <c r="A694" t="s">
         <v>438</v>
       </c>
@@ -25004,7 +25052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="695" spans="1:15" hidden="1">
+    <row r="695" spans="1:15">
       <c r="A695" t="s">
         <v>460</v>
       </c>
@@ -25033,7 +25081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="696" spans="1:15" hidden="1">
+    <row r="696" spans="1:15">
       <c r="A696" t="s">
         <v>1009</v>
       </c>
@@ -25062,7 +25110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="697" spans="1:15" hidden="1">
+    <row r="697" spans="1:15">
       <c r="A697" t="s">
         <v>1010</v>
       </c>
@@ -25091,7 +25139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="698" spans="1:15" hidden="1">
+    <row r="698" spans="1:15">
       <c r="A698" t="s">
         <v>1013</v>
       </c>
@@ -25120,7 +25168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="699" spans="1:15" hidden="1">
+    <row r="699" spans="1:15">
       <c r="A699" t="s">
         <v>645</v>
       </c>
@@ -25149,7 +25197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="700" spans="1:15" hidden="1">
+    <row r="700" spans="1:15">
       <c r="A700" t="s">
         <v>1017</v>
       </c>
@@ -25178,7 +25226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="701" spans="1:15" hidden="1">
+    <row r="701" spans="1:15">
       <c r="A701" t="s">
         <v>913</v>
       </c>
@@ -25207,7 +25255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="702" spans="1:15" hidden="1">
+    <row r="702" spans="1:15">
       <c r="A702" t="s">
         <v>1022</v>
       </c>
@@ -25236,7 +25284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="703" spans="1:15" hidden="1">
+    <row r="703" spans="1:15">
       <c r="A703" t="s">
         <v>925</v>
       </c>
@@ -25265,7 +25313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="704" spans="1:15" hidden="1">
+    <row r="704" spans="1:15">
       <c r="A704" t="s">
         <v>1009</v>
       </c>
@@ -25294,7 +25342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="705" spans="1:15" hidden="1">
+    <row r="705" spans="1:15">
       <c r="A705" t="s">
         <v>86</v>
       </c>
@@ -25323,7 +25371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="706" spans="1:15" hidden="1">
+    <row r="706" spans="1:15">
       <c r="A706" t="s">
         <v>1030</v>
       </c>
@@ -25352,7 +25400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="707" spans="1:15" hidden="1">
+    <row r="707" spans="1:15">
       <c r="A707" t="s">
         <v>105</v>
       </c>
@@ -25381,7 +25429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:15" hidden="1">
+    <row r="708" spans="1:15">
       <c r="A708" t="s">
         <v>945</v>
       </c>
@@ -25410,7 +25458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="709" spans="1:15" hidden="1">
+    <row r="709" spans="1:15">
       <c r="A709" t="s">
         <v>946</v>
       </c>
@@ -25439,7 +25487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="710" spans="1:15" hidden="1">
+    <row r="710" spans="1:15">
       <c r="A710" t="s">
         <v>886</v>
       </c>
@@ -25468,7 +25516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="711" spans="1:15" hidden="1">
+    <row r="711" spans="1:15">
       <c r="A711" t="s">
         <v>947</v>
       </c>
@@ -25497,7 +25545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="712" spans="1:15" hidden="1">
+    <row r="712" spans="1:15">
       <c r="A712" t="s">
         <v>948</v>
       </c>
@@ -25526,7 +25574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="713" spans="1:15" hidden="1">
+    <row r="713" spans="1:15">
       <c r="A713" t="s">
         <v>1033</v>
       </c>
@@ -25555,7 +25603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="714" spans="1:15" hidden="1">
+    <row r="714" spans="1:15">
       <c r="A714" t="s">
         <v>1035</v>
       </c>
@@ -25584,7 +25632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="715" spans="1:15" hidden="1">
+    <row r="715" spans="1:15">
       <c r="A715" t="s">
         <v>1038</v>
       </c>
@@ -25613,7 +25661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="716" spans="1:15" hidden="1">
+    <row r="716" spans="1:15">
       <c r="A716" t="s">
         <v>1040</v>
       </c>
@@ -25642,7 +25690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="717" spans="1:15" hidden="1">
+    <row r="717" spans="1:15">
       <c r="A717" t="s">
         <v>1041</v>
       </c>
@@ -25671,7 +25719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="718" spans="1:15" hidden="1">
+    <row r="718" spans="1:15">
       <c r="A718" t="s">
         <v>798</v>
       </c>
@@ -25700,7 +25748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="719" spans="1:15" hidden="1">
+    <row r="719" spans="1:15">
       <c r="A719" t="s">
         <v>1046</v>
       </c>
@@ -25729,7 +25777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="720" spans="1:15" hidden="1">
+    <row r="720" spans="1:15">
       <c r="A720" t="s">
         <v>1049</v>
       </c>
@@ -25758,7 +25806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="721" spans="1:15" hidden="1">
+    <row r="721" spans="1:15">
       <c r="A721" t="s">
         <v>913</v>
       </c>
@@ -25787,7 +25835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="722" spans="1:15" hidden="1">
+    <row r="722" spans="1:15">
       <c r="A722" t="s">
         <v>915</v>
       </c>
@@ -25853,6 +25901,9 @@
       <c r="L723" t="s">
         <v>31</v>
       </c>
+      <c r="M723" t="s">
+        <v>20</v>
+      </c>
       <c r="N723">
         <v>2020</v>
       </c>
@@ -25877,7 +25928,7 @@
         <v>45859</v>
       </c>
       <c r="F724" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G724" t="s">
         <v>20</v>
@@ -25892,7 +25943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="725" spans="1:15" hidden="1">
+    <row r="725" spans="1:15">
       <c r="A725" t="s">
         <v>1056</v>
       </c>
@@ -25921,7 +25972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="726" spans="1:15" hidden="1">
+    <row r="726" spans="1:15">
       <c r="A726" t="s">
         <v>1059</v>
       </c>
@@ -25950,7 +26001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="727" spans="1:15" hidden="1">
+    <row r="727" spans="1:15">
       <c r="A727" t="s">
         <v>1062</v>
       </c>
@@ -25979,7 +26030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="728" spans="1:15" hidden="1">
+    <row r="728" spans="1:15">
       <c r="A728" t="s">
         <v>1065</v>
       </c>
@@ -26008,7 +26059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="729" spans="1:15" hidden="1">
+    <row r="729" spans="1:15">
       <c r="A729" t="s">
         <v>1066</v>
       </c>
@@ -26037,7 +26088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="730" spans="1:15" hidden="1">
+    <row r="730" spans="1:15">
       <c r="A730" t="s">
         <v>1066</v>
       </c>
@@ -26103,6 +26154,9 @@
       <c r="L731" t="s">
         <v>1070</v>
       </c>
+      <c r="M731" t="s">
+        <v>20</v>
+      </c>
       <c r="N731">
         <v>2018</v>
       </c>
@@ -26147,6 +26201,9 @@
       <c r="L732" t="s">
         <v>1070</v>
       </c>
+      <c r="M732" t="s">
+        <v>20</v>
+      </c>
       <c r="N732">
         <v>2018</v>
       </c>
@@ -26154,7 +26211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="733" spans="1:15" hidden="1">
+    <row r="733" spans="1:15">
       <c r="A733" t="s">
         <v>1066</v>
       </c>
@@ -26171,7 +26228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="734" spans="1:15" hidden="1">
+    <row r="734" spans="1:15">
       <c r="A734" t="s">
         <v>1073</v>
       </c>
@@ -26200,7 +26257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="735" spans="1:15" hidden="1">
+    <row r="735" spans="1:15">
       <c r="A735" t="s">
         <v>1073</v>
       </c>
@@ -26217,7 +26274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="736" spans="1:15" hidden="1">
+    <row r="736" spans="1:15">
       <c r="A736" t="s">
         <v>1076</v>
       </c>
@@ -26246,7 +26303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="737" spans="1:15" hidden="1">
+    <row r="737" spans="1:15">
       <c r="A737" t="s">
         <v>1076</v>
       </c>
@@ -26275,7 +26332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="738" spans="1:15" hidden="1">
+    <row r="738" spans="1:15">
       <c r="A738" t="s">
         <v>1076</v>
       </c>
@@ -26304,7 +26361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="739" spans="1:15" hidden="1">
+    <row r="739" spans="1:15">
       <c r="A739" t="s">
         <v>1076</v>
       </c>
@@ -26333,7 +26390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="740" spans="1:15" hidden="1">
+    <row r="740" spans="1:15">
       <c r="A740" t="s">
         <v>1081</v>
       </c>
@@ -26362,7 +26419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="741" spans="1:15" hidden="1">
+    <row r="741" spans="1:15">
       <c r="A741" t="s">
         <v>1083</v>
       </c>
@@ -26391,7 +26448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="742" spans="1:15" hidden="1">
+    <row r="742" spans="1:15">
       <c r="A742" t="s">
         <v>1086</v>
       </c>
@@ -26420,7 +26477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="743" spans="1:15" hidden="1">
+    <row r="743" spans="1:15">
       <c r="A743" t="s">
         <v>373</v>
       </c>
@@ -26449,7 +26506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="744" spans="1:15" hidden="1">
+    <row r="744" spans="1:15">
       <c r="A744" t="s">
         <v>509</v>
       </c>
@@ -26478,7 +26535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="745" spans="1:15" hidden="1">
+    <row r="745" spans="1:15">
       <c r="A745" t="s">
         <v>404</v>
       </c>
@@ -26507,7 +26564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="746" spans="1:15" hidden="1">
+    <row r="746" spans="1:15">
       <c r="A746" t="s">
         <v>86</v>
       </c>
@@ -26536,7 +26593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="747" spans="1:15" hidden="1">
+    <row r="747" spans="1:15">
       <c r="A747" t="s">
         <v>438</v>
       </c>
@@ -26565,7 +26622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="748" spans="1:15" hidden="1">
+    <row r="748" spans="1:15">
       <c r="A748" t="s">
         <v>396</v>
       </c>
@@ -26594,7 +26651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="749" spans="1:15" hidden="1">
+    <row r="749" spans="1:15">
       <c r="A749" t="s">
         <v>109</v>
       </c>
@@ -26623,7 +26680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="750" spans="1:15" hidden="1">
+    <row r="750" spans="1:15">
       <c r="A750" t="s">
         <v>134</v>
       </c>
@@ -26652,7 +26709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="751" spans="1:15" hidden="1">
+    <row r="751" spans="1:15">
       <c r="A751" t="s">
         <v>358</v>
       </c>
@@ -26681,7 +26738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="752" spans="1:15" hidden="1">
+    <row r="752" spans="1:15">
       <c r="A752" t="s">
         <v>109</v>
       </c>
@@ -26710,7 +26767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="753" spans="1:15" hidden="1">
+    <row r="753" spans="1:15">
       <c r="A753" t="s">
         <v>299</v>
       </c>
@@ -26739,7 +26796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="754" spans="1:15" hidden="1">
+    <row r="754" spans="1:15">
       <c r="A754" t="s">
         <v>404</v>
       </c>
@@ -26768,7 +26825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="755" spans="1:15" hidden="1">
+    <row r="755" spans="1:15">
       <c r="A755" t="s">
         <v>358</v>
       </c>
@@ -26797,7 +26854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="756" spans="1:15" hidden="1">
+    <row r="756" spans="1:15">
       <c r="A756" t="s">
         <v>196</v>
       </c>
@@ -26826,7 +26883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="757" spans="1:15" hidden="1">
+    <row r="757" spans="1:15">
       <c r="A757" t="s">
         <v>358</v>
       </c>
@@ -26855,7 +26912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="758" spans="1:15" hidden="1">
+    <row r="758" spans="1:15">
       <c r="A758" t="s">
         <v>167</v>
       </c>
@@ -26884,7 +26941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="759" spans="1:15" hidden="1">
+    <row r="759" spans="1:15">
       <c r="A759" t="s">
         <v>196</v>
       </c>
@@ -26913,7 +26970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="760" spans="1:15" hidden="1">
+    <row r="760" spans="1:15">
       <c r="A760" t="s">
         <v>196</v>
       </c>
@@ -26942,7 +26999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="761" spans="1:15" hidden="1">
+    <row r="761" spans="1:15">
       <c r="A761" t="s">
         <v>1073</v>
       </c>
@@ -26971,7 +27028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="762" spans="1:15" hidden="1">
+    <row r="762" spans="1:15">
       <c r="A762" t="s">
         <v>1073</v>
       </c>
@@ -27000,7 +27057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="763" spans="1:15" hidden="1">
+    <row r="763" spans="1:15">
       <c r="A763" t="s">
         <v>358</v>
       </c>
@@ -27029,7 +27086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="764" spans="1:15" hidden="1">
+    <row r="764" spans="1:15">
       <c r="A764" t="s">
         <v>196</v>
       </c>
@@ -27058,7 +27115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="765" spans="1:15" hidden="1">
+    <row r="765" spans="1:15">
       <c r="A765" t="s">
         <v>408</v>
       </c>
@@ -27087,7 +27144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="766" spans="1:15" hidden="1">
+    <row r="766" spans="1:15">
       <c r="A766" t="s">
         <v>408</v>
       </c>
@@ -27116,7 +27173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="767" spans="1:15" hidden="1">
+    <row r="767" spans="1:15">
       <c r="A767" t="s">
         <v>408</v>
       </c>
@@ -27145,7 +27202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="768" spans="1:15" hidden="1">
+    <row r="768" spans="1:15">
       <c r="A768" t="s">
         <v>408</v>
       </c>
@@ -27174,7 +27231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="769" spans="1:15" hidden="1">
+    <row r="769" spans="1:15">
       <c r="A769" t="s">
         <v>408</v>
       </c>
@@ -27203,7 +27260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="770" spans="1:15" hidden="1">
+    <row r="770" spans="1:15">
       <c r="A770" t="s">
         <v>89</v>
       </c>
@@ -27232,7 +27289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="771" spans="1:15" hidden="1">
+    <row r="771" spans="1:15">
       <c r="A771" t="s">
         <v>89</v>
       </c>
@@ -27261,7 +27318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="772" spans="1:15" hidden="1">
+    <row r="772" spans="1:15">
       <c r="A772" t="s">
         <v>89</v>
       </c>
@@ -27290,7 +27347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="773" spans="1:15" hidden="1">
+    <row r="773" spans="1:15">
       <c r="A773" t="s">
         <v>89</v>
       </c>
@@ -27319,7 +27376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="774" spans="1:15" hidden="1">
+    <row r="774" spans="1:15">
       <c r="A774" t="s">
         <v>89</v>
       </c>
@@ -27348,7 +27405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="775" spans="1:15" hidden="1">
+    <row r="775" spans="1:15">
       <c r="A775" t="s">
         <v>89</v>
       </c>
@@ -27377,7 +27434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="776" spans="1:15" hidden="1">
+    <row r="776" spans="1:15">
       <c r="A776" t="s">
         <v>89</v>
       </c>
@@ -27406,7 +27463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="777" spans="1:15" hidden="1">
+    <row r="777" spans="1:15">
       <c r="A777" t="s">
         <v>408</v>
       </c>
@@ -27435,7 +27492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="778" spans="1:15" hidden="1">
+    <row r="778" spans="1:15">
       <c r="A778" t="s">
         <v>337</v>
       </c>
@@ -27464,7 +27521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="779" spans="1:15" hidden="1">
+    <row r="779" spans="1:15">
       <c r="A779" t="s">
         <v>408</v>
       </c>
@@ -27493,7 +27550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="780" spans="1:15" hidden="1">
+    <row r="780" spans="1:15">
       <c r="A780" t="s">
         <v>408</v>
       </c>
@@ -27522,7 +27579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="781" spans="1:15" hidden="1">
+    <row r="781" spans="1:15">
       <c r="A781" t="s">
         <v>408</v>
       </c>
@@ -27551,7 +27608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="782" spans="1:15" hidden="1">
+    <row r="782" spans="1:15">
       <c r="A782" t="s">
         <v>408</v>
       </c>
@@ -27580,7 +27637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="783" spans="1:15" hidden="1">
+    <row r="783" spans="1:15">
       <c r="A783" t="s">
         <v>278</v>
       </c>
@@ -27609,7 +27666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="784" spans="1:15" hidden="1">
+    <row r="784" spans="1:15">
       <c r="A784" t="s">
         <v>279</v>
       </c>
@@ -27638,7 +27695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="785" spans="1:16" hidden="1">
+    <row r="785" spans="1:16">
       <c r="A785" t="s">
         <v>408</v>
       </c>
@@ -27667,7 +27724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="786" spans="1:16" hidden="1">
+    <row r="786" spans="1:16">
       <c r="A786" t="s">
         <v>408</v>
       </c>
@@ -27696,7 +27753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="787" spans="1:16" hidden="1">
+    <row r="787" spans="1:16">
       <c r="A787" t="s">
         <v>408</v>
       </c>
@@ -27725,7 +27782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="788" spans="1:16" hidden="1">
+    <row r="788" spans="1:16">
       <c r="A788" t="s">
         <v>1127</v>
       </c>
@@ -27791,6 +27848,9 @@
       <c r="L789" t="s">
         <v>31</v>
       </c>
+      <c r="M789" t="s">
+        <v>20</v>
+      </c>
       <c r="N789">
         <v>2010</v>
       </c>
@@ -27801,7 +27861,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="790" spans="1:16" hidden="1">
+    <row r="790" spans="1:16">
       <c r="A790" t="s">
         <v>1132</v>
       </c>
@@ -27830,7 +27890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="791" spans="1:16" hidden="1">
+    <row r="791" spans="1:16">
       <c r="A791" t="s">
         <v>530</v>
       </c>
@@ -27859,7 +27919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="792" spans="1:16" hidden="1">
+    <row r="792" spans="1:16">
       <c r="A792" t="s">
         <v>234</v>
       </c>
@@ -27888,7 +27948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="793" spans="1:16" hidden="1">
+    <row r="793" spans="1:16">
       <c r="A793" t="s">
         <v>438</v>
       </c>
@@ -27917,7 +27977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="794" spans="1:16" hidden="1">
+    <row r="794" spans="1:16">
       <c r="A794" t="s">
         <v>460</v>
       </c>
@@ -27946,7 +28006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="795" spans="1:16" hidden="1">
+    <row r="795" spans="1:16">
       <c r="A795" t="s">
         <v>1009</v>
       </c>
@@ -27975,7 +28035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="796" spans="1:16" hidden="1">
+    <row r="796" spans="1:16">
       <c r="A796" t="s">
         <v>1137</v>
       </c>
@@ -28004,7 +28064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="797" spans="1:16" hidden="1">
+    <row r="797" spans="1:16">
       <c r="A797" t="s">
         <v>1140</v>
       </c>
@@ -28033,7 +28093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="798" spans="1:16" hidden="1">
+    <row r="798" spans="1:16">
       <c r="A798" t="s">
         <v>1143</v>
       </c>
@@ -28062,7 +28122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="799" spans="1:16" hidden="1">
+    <row r="799" spans="1:16">
       <c r="A799" t="s">
         <v>1146</v>
       </c>
@@ -28091,7 +28151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="800" spans="1:16" hidden="1">
+    <row r="800" spans="1:16">
       <c r="A800" t="s">
         <v>1147</v>
       </c>
@@ -28120,7 +28180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="801" spans="1:15" hidden="1">
+    <row r="801" spans="1:15">
       <c r="A801" t="s">
         <v>1148</v>
       </c>
@@ -28149,7 +28209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="802" spans="1:15" hidden="1">
+    <row r="802" spans="1:15">
       <c r="A802" t="s">
         <v>1149</v>
       </c>
@@ -28178,7 +28238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="803" spans="1:15" hidden="1">
+    <row r="803" spans="1:15">
       <c r="A803" t="s">
         <v>1150</v>
       </c>
@@ -28207,7 +28267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="804" spans="1:15" hidden="1">
+    <row r="804" spans="1:15">
       <c r="A804" t="s">
         <v>1151</v>
       </c>
@@ -28236,7 +28296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="805" spans="1:15" hidden="1">
+    <row r="805" spans="1:15">
       <c r="A805" t="s">
         <v>1152</v>
       </c>
@@ -28265,7 +28325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="806" spans="1:15" hidden="1">
+    <row r="806" spans="1:15">
       <c r="A806" t="s">
         <v>527</v>
       </c>
@@ -28294,7 +28354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="807" spans="1:15" hidden="1">
+    <row r="807" spans="1:15">
       <c r="A807" t="s">
         <v>360</v>
       </c>
@@ -28323,7 +28383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="808" spans="1:15" hidden="1">
+    <row r="808" spans="1:15">
       <c r="A808" t="s">
         <v>193</v>
       </c>
@@ -28352,7 +28412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="809" spans="1:15" hidden="1">
+    <row r="809" spans="1:15">
       <c r="A809" t="s">
         <v>360</v>
       </c>
@@ -28381,7 +28441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="810" spans="1:15" hidden="1">
+    <row r="810" spans="1:15">
       <c r="A810" t="s">
         <v>1159</v>
       </c>
@@ -28410,7 +28470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="811" spans="1:15" hidden="1">
+    <row r="811" spans="1:15">
       <c r="A811" t="s">
         <v>1160</v>
       </c>
@@ -28439,7 +28499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="812" spans="1:15" hidden="1">
+    <row r="812" spans="1:15">
       <c r="A812" t="s">
         <v>1161</v>
       </c>
@@ -28468,7 +28528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="813" spans="1:15" hidden="1">
+    <row r="813" spans="1:15">
       <c r="A813" t="s">
         <v>1056</v>
       </c>
@@ -28497,7 +28557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="814" spans="1:15" hidden="1">
+    <row r="814" spans="1:15">
       <c r="A814" t="s">
         <v>1166</v>
       </c>
@@ -28526,7 +28586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="815" spans="1:15" hidden="1">
+    <row r="815" spans="1:15">
       <c r="A815" t="s">
         <v>971</v>
       </c>
@@ -28555,7 +28615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="816" spans="1:15" hidden="1">
+    <row r="816" spans="1:15">
       <c r="A816" t="s">
         <v>1168</v>
       </c>
@@ -28584,7 +28644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="817" spans="1:15" hidden="1">
+    <row r="817" spans="1:15">
       <c r="A817" t="s">
         <v>1171</v>
       </c>
@@ -28613,7 +28673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="818" spans="1:15" hidden="1">
+    <row r="818" spans="1:15">
       <c r="A818" t="s">
         <v>968</v>
       </c>
@@ -28642,7 +28702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="819" spans="1:15" hidden="1">
+    <row r="819" spans="1:15">
       <c r="A819" t="s">
         <v>968</v>
       </c>
@@ -28708,6 +28768,9 @@
       <c r="L820" t="s">
         <v>31</v>
       </c>
+      <c r="M820" t="s">
+        <v>20</v>
+      </c>
       <c r="N820">
         <v>2015</v>
       </c>
@@ -28715,7 +28778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="821" spans="1:15" hidden="1">
+    <row r="821" spans="1:15">
       <c r="A821" t="s">
         <v>1178</v>
       </c>
@@ -28744,7 +28807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="822" spans="1:15" hidden="1">
+    <row r="822" spans="1:15">
       <c r="A822" t="s">
         <v>1180</v>
       </c>
@@ -28773,7 +28836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="823" spans="1:15" hidden="1">
+    <row r="823" spans="1:15">
       <c r="A823" t="s">
         <v>1152</v>
       </c>
@@ -28802,7 +28865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="824" spans="1:15" hidden="1">
+    <row r="824" spans="1:15">
       <c r="A824" t="s">
         <v>105</v>
       </c>
@@ -28831,7 +28894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="825" spans="1:15" hidden="1">
+    <row r="825" spans="1:15">
       <c r="A825" t="s">
         <v>1186</v>
       </c>
@@ -28860,7 +28923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="826" spans="1:15" hidden="1">
+    <row r="826" spans="1:15">
       <c r="A826" t="s">
         <v>1188</v>
       </c>
@@ -28889,7 +28952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="827" spans="1:15" hidden="1">
+    <row r="827" spans="1:15">
       <c r="A827" t="s">
         <v>943</v>
       </c>
@@ -28918,7 +28981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="828" spans="1:15" hidden="1">
+    <row r="828" spans="1:15">
       <c r="A828" t="s">
         <v>1191</v>
       </c>
@@ -28947,7 +29010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="829" spans="1:15" hidden="1">
+    <row r="829" spans="1:15">
       <c r="A829" t="s">
         <v>1194</v>
       </c>
@@ -28976,7 +29039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="830" spans="1:15" hidden="1">
+    <row r="830" spans="1:15">
       <c r="A830" t="s">
         <v>1195</v>
       </c>
@@ -29005,7 +29068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="831" spans="1:15" hidden="1">
+    <row r="831" spans="1:15">
       <c r="A831" t="s">
         <v>1198</v>
       </c>
@@ -29034,7 +29097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="832" spans="1:15" hidden="1">
+    <row r="832" spans="1:15">
       <c r="A832" t="s">
         <v>1198</v>
       </c>
@@ -29063,7 +29126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="833" spans="1:15" hidden="1">
+    <row r="833" spans="1:15">
       <c r="A833" t="s">
         <v>1202</v>
       </c>
@@ -29092,7 +29155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="834" spans="1:15" hidden="1">
+    <row r="834" spans="1:15">
       <c r="A834" t="s">
         <v>1204</v>
       </c>
@@ -29158,6 +29221,9 @@
       <c r="L835" t="s">
         <v>31</v>
       </c>
+      <c r="M835" t="s">
+        <v>20</v>
+      </c>
       <c r="N835">
         <v>2020</v>
       </c>
@@ -29165,7 +29231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="836" spans="1:15" hidden="1">
+    <row r="836" spans="1:15">
       <c r="A836" t="s">
         <v>63</v>
       </c>
@@ -29194,7 +29260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="837" spans="1:15" hidden="1">
+    <row r="837" spans="1:15">
       <c r="A837" t="s">
         <v>279</v>
       </c>
@@ -29223,7 +29289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="838" spans="1:15" hidden="1">
+    <row r="838" spans="1:15">
       <c r="A838" t="s">
         <v>697</v>
       </c>
@@ -29252,7 +29318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="839" spans="1:15" hidden="1">
+    <row r="839" spans="1:15">
       <c r="A839" t="s">
         <v>1211</v>
       </c>
@@ -29281,7 +29347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="840" spans="1:15" hidden="1">
+    <row r="840" spans="1:15">
       <c r="A840" t="s">
         <v>965</v>
       </c>
@@ -29310,7 +29376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="841" spans="1:15" hidden="1">
+    <row r="841" spans="1:15">
       <c r="A841" t="s">
         <v>1129</v>
       </c>
@@ -29339,7 +29405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="842" spans="1:15" hidden="1">
+    <row r="842" spans="1:15">
       <c r="A842" t="s">
         <v>1216</v>
       </c>
@@ -29368,7 +29434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="843" spans="1:15" hidden="1">
+    <row r="843" spans="1:15">
       <c r="A843" t="s">
         <v>213</v>
       </c>
@@ -29434,6 +29500,9 @@
       <c r="L844" t="s">
         <v>31</v>
       </c>
+      <c r="M844" t="s">
+        <v>20</v>
+      </c>
       <c r="N844">
         <v>2020</v>
       </c>
@@ -29441,7 +29510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="845" spans="1:15" hidden="1">
+    <row r="845" spans="1:15">
       <c r="A845" t="s">
         <v>1222</v>
       </c>
@@ -29470,7 +29539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="846" spans="1:15" hidden="1">
+    <row r="846" spans="1:15">
       <c r="A846" t="s">
         <v>1225</v>
       </c>
@@ -29499,7 +29568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="847" spans="1:15" hidden="1">
+    <row r="847" spans="1:15">
       <c r="A847" t="s">
         <v>1228</v>
       </c>
@@ -29528,7 +29597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="848" spans="1:15" hidden="1">
+    <row r="848" spans="1:15">
       <c r="A848" t="s">
         <v>319</v>
       </c>
@@ -29557,7 +29626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="849" spans="1:15" hidden="1">
+    <row r="849" spans="1:15">
       <c r="A849" t="s">
         <v>928</v>
       </c>
@@ -29571,7 +29640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="850" spans="1:15" hidden="1">
+    <row r="850" spans="1:15">
       <c r="A850" t="s">
         <v>1232</v>
       </c>
@@ -29585,7 +29654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="851" spans="1:15" hidden="1">
+    <row r="851" spans="1:15">
       <c r="A851" t="s">
         <v>928</v>
       </c>
@@ -29614,7 +29683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="852" spans="1:15" hidden="1">
+    <row r="852" spans="1:15">
       <c r="A852" t="s">
         <v>213</v>
       </c>
@@ -29643,7 +29712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="853" spans="1:15" hidden="1">
+    <row r="853" spans="1:15">
       <c r="A853" t="s">
         <v>1236</v>
       </c>
@@ -29660,7 +29729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="854" spans="1:15" hidden="1">
+    <row r="854" spans="1:15">
       <c r="A854" t="s">
         <v>832</v>
       </c>
@@ -29689,7 +29758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="855" spans="1:15" hidden="1">
+    <row r="855" spans="1:15">
       <c r="A855" t="s">
         <v>213</v>
       </c>
@@ -29706,7 +29775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="856" spans="1:15" hidden="1">
+    <row r="856" spans="1:15">
       <c r="A856" t="s">
         <v>1240</v>
       </c>
@@ -29735,7 +29804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="857" spans="1:15" hidden="1">
+    <row r="857" spans="1:15">
       <c r="A857" t="s">
         <v>1242</v>
       </c>
@@ -29764,7 +29833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="858" spans="1:15" hidden="1">
+    <row r="858" spans="1:15">
       <c r="A858" t="s">
         <v>1244</v>
       </c>
@@ -29793,7 +29862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="859" spans="1:15" hidden="1">
+    <row r="859" spans="1:15">
       <c r="A859" t="s">
         <v>1246</v>
       </c>
@@ -29810,7 +29879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="860" spans="1:15" hidden="1">
+    <row r="860" spans="1:15">
       <c r="A860" t="s">
         <v>1248</v>
       </c>
@@ -29827,7 +29896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="861" spans="1:15" hidden="1">
+    <row r="861" spans="1:15">
       <c r="A861" t="s">
         <v>279</v>
       </c>
@@ -29844,7 +29913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="862" spans="1:15" hidden="1">
+    <row r="862" spans="1:15">
       <c r="A862" t="s">
         <v>289</v>
       </c>
@@ -29861,7 +29930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="863" spans="1:15" hidden="1">
+    <row r="863" spans="1:15">
       <c r="A863" t="s">
         <v>1249</v>
       </c>
@@ -29878,7 +29947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="864" spans="1:15" hidden="1">
+    <row r="864" spans="1:15">
       <c r="A864" t="s">
         <v>1250</v>
       </c>
@@ -29895,7 +29964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="865" spans="1:16" hidden="1">
+    <row r="865" spans="1:16">
       <c r="A865" t="s">
         <v>1251</v>
       </c>
@@ -29912,7 +29981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="866" spans="1:16" hidden="1">
+    <row r="866" spans="1:16">
       <c r="A866" t="s">
         <v>1252</v>
       </c>
@@ -29929,7 +29998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="867" spans="1:16" hidden="1">
+    <row r="867" spans="1:16">
       <c r="A867" t="s">
         <v>1253</v>
       </c>
@@ -29946,7 +30015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="868" spans="1:16" hidden="1">
+    <row r="868" spans="1:16">
       <c r="A868" t="s">
         <v>1254</v>
       </c>
@@ -29975,47 +30044,53 @@
         <v>0</v>
       </c>
     </row>
-    <row r="869" spans="1:16" s="6" customFormat="1">
-      <c r="A869" s="6" t="s">
+    <row r="869" spans="1:16">
+      <c r="A869" t="s">
         <v>77</v>
       </c>
-      <c r="B869" s="6" t="s">
+      <c r="B869" t="s">
         <v>1256</v>
       </c>
-      <c r="C869" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D869" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E869" s="8">
+      <c r="C869" t="s">
+        <v>17</v>
+      </c>
+      <c r="D869" t="s">
+        <v>35</v>
+      </c>
+      <c r="E869" s="1">
         <v>45869</v>
       </c>
-      <c r="F869" s="6" t="s">
+      <c r="F869" t="s">
         <v>5</v>
       </c>
-      <c r="G869" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H869" s="6" t="s">
+      <c r="G869" t="s">
+        <v>20</v>
+      </c>
+      <c r="H869" t="s">
         <v>1257</v>
       </c>
-      <c r="I869" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J869" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K869" s="6" t="s">
+      <c r="I869" t="s">
+        <v>20</v>
+      </c>
+      <c r="J869" t="s">
+        <v>20</v>
+      </c>
+      <c r="K869" t="s">
         <v>31</v>
       </c>
-      <c r="L869" s="6" t="s">
+      <c r="L869" t="s">
         <v>31</v>
       </c>
-      <c r="O869" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P869" s="6" t="s">
+      <c r="M869" t="s">
+        <v>765</v>
+      </c>
+      <c r="N869">
+        <v>2019</v>
+      </c>
+      <c r="O869" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P869" t="s">
         <v>1258</v>
       </c>
     </row>
@@ -30056,6 +30131,9 @@
       <c r="L870" t="s">
         <v>31</v>
       </c>
+      <c r="M870" t="s">
+        <v>20</v>
+      </c>
       <c r="N870">
         <v>2022</v>
       </c>
@@ -30100,6 +30178,9 @@
       <c r="L871" t="s">
         <v>31</v>
       </c>
+      <c r="M871" t="s">
+        <v>20</v>
+      </c>
       <c r="N871">
         <v>2022</v>
       </c>
@@ -30144,6 +30225,9 @@
       <c r="L872" t="s">
         <v>31</v>
       </c>
+      <c r="M872" t="s">
+        <v>20</v>
+      </c>
       <c r="N872">
         <v>2022</v>
       </c>
@@ -30151,7 +30235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="873" spans="1:16" hidden="1">
+    <row r="873" spans="1:16">
       <c r="A873" t="s">
         <v>1263</v>
       </c>
@@ -30180,7 +30264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="874" spans="1:16" hidden="1">
+    <row r="874" spans="1:16">
       <c r="A874" t="s">
         <v>530</v>
       </c>
@@ -30209,7 +30293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="875" spans="1:16" hidden="1">
+    <row r="875" spans="1:16">
       <c r="A875" t="s">
         <v>1267</v>
       </c>
@@ -30238,7 +30322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="876" spans="1:16" hidden="1">
+    <row r="876" spans="1:16">
       <c r="A876" t="s">
         <v>1269</v>
       </c>
@@ -30267,7 +30351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="877" spans="1:16" hidden="1">
+    <row r="877" spans="1:16">
       <c r="A877" t="s">
         <v>1270</v>
       </c>
@@ -30296,7 +30380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="878" spans="1:16" hidden="1">
+    <row r="878" spans="1:16">
       <c r="A878" t="s">
         <v>530</v>
       </c>
@@ -30325,7 +30409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="879" spans="1:16" hidden="1">
+    <row r="879" spans="1:16">
       <c r="A879" t="s">
         <v>1273</v>
       </c>
@@ -30354,7 +30438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="880" spans="1:16" hidden="1">
+    <row r="880" spans="1:16">
       <c r="A880" t="s">
         <v>1276</v>
       </c>
@@ -30383,7 +30467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="881" spans="1:15" hidden="1">
+    <row r="881" spans="1:15">
       <c r="A881" t="s">
         <v>1277</v>
       </c>
@@ -30412,7 +30496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="882" spans="1:15" hidden="1">
+    <row r="882" spans="1:15">
       <c r="A882" t="s">
         <v>63</v>
       </c>
@@ -30444,7 +30528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="883" spans="1:15" hidden="1">
+    <row r="883" spans="1:15">
       <c r="A883" t="s">
         <v>63</v>
       </c>
@@ -30473,7 +30557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="884" spans="1:15" hidden="1">
+    <row r="884" spans="1:15">
       <c r="A884" t="s">
         <v>1282</v>
       </c>
@@ -30502,7 +30586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="885" spans="1:15" hidden="1">
+    <row r="885" spans="1:15">
       <c r="A885" t="s">
         <v>44</v>
       </c>
@@ -30531,7 +30615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="886" spans="1:15" hidden="1">
+    <row r="886" spans="1:15">
       <c r="A886" t="s">
         <v>1286</v>
       </c>
@@ -30560,7 +30644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="887" spans="1:15" hidden="1">
+    <row r="887" spans="1:15">
       <c r="A887" t="s">
         <v>1289</v>
       </c>
@@ -30589,7 +30673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="888" spans="1:15" hidden="1">
+    <row r="888" spans="1:15">
       <c r="A888" t="s">
         <v>1291</v>
       </c>
@@ -30618,7 +30702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="889" spans="1:15" hidden="1">
+    <row r="889" spans="1:15">
       <c r="A889" t="s">
         <v>1291</v>
       </c>
@@ -30647,7 +30731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="890" spans="1:15" hidden="1">
+    <row r="890" spans="1:15">
       <c r="A890" t="s">
         <v>1293</v>
       </c>
@@ -30676,7 +30760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="891" spans="1:15" hidden="1">
+    <row r="891" spans="1:15">
       <c r="A891" t="s">
         <v>193</v>
       </c>
@@ -30705,7 +30789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="892" spans="1:15" hidden="1">
+    <row r="892" spans="1:15">
       <c r="A892" t="s">
         <v>1296</v>
       </c>
@@ -30734,7 +30818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="893" spans="1:15" hidden="1">
+    <row r="893" spans="1:15">
       <c r="A893" t="s">
         <v>647</v>
       </c>
@@ -30763,7 +30847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="894" spans="1:15" hidden="1">
+    <row r="894" spans="1:15">
       <c r="A894" t="s">
         <v>1300</v>
       </c>
@@ -30792,7 +30876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="895" spans="1:15" hidden="1">
+    <row r="895" spans="1:15">
       <c r="A895" t="s">
         <v>1302</v>
       </c>
@@ -30821,7 +30905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="896" spans="1:15" hidden="1">
+    <row r="896" spans="1:15">
       <c r="A896" t="s">
         <v>1303</v>
       </c>
@@ -30850,7 +30934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="897" spans="1:15" hidden="1">
+    <row r="897" spans="1:15">
       <c r="A897" t="s">
         <v>1305</v>
       </c>
@@ -30879,7 +30963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="898" spans="1:15" hidden="1">
+    <row r="898" spans="1:15">
       <c r="A898" t="s">
         <v>1307</v>
       </c>
@@ -30908,7 +30992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="899" spans="1:15" hidden="1">
+    <row r="899" spans="1:15">
       <c r="A899" t="s">
         <v>1309</v>
       </c>
@@ -30937,7 +31021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="900" spans="1:15" hidden="1">
+    <row r="900" spans="1:15">
       <c r="A900" t="s">
         <v>1311</v>
       </c>
@@ -30966,7 +31050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="901" spans="1:15" hidden="1">
+    <row r="901" spans="1:15">
       <c r="A901" t="s">
         <v>1296</v>
       </c>
@@ -30995,7 +31079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="902" spans="1:15" hidden="1">
+    <row r="902" spans="1:15">
       <c r="A902" t="s">
         <v>140</v>
       </c>
@@ -31024,7 +31108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="903" spans="1:15" hidden="1">
+    <row r="903" spans="1:15">
       <c r="A903" t="s">
         <v>1315</v>
       </c>
@@ -31053,7 +31137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="904" spans="1:15" hidden="1">
+    <row r="904" spans="1:15">
       <c r="A904" t="s">
         <v>1317</v>
       </c>
@@ -31082,7 +31166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="905" spans="1:15" hidden="1">
+    <row r="905" spans="1:15">
       <c r="A905" t="s">
         <v>1318</v>
       </c>
@@ -31111,7 +31195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="906" spans="1:15" hidden="1">
+    <row r="906" spans="1:15">
       <c r="A906" t="s">
         <v>886</v>
       </c>
@@ -31140,7 +31224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="907" spans="1:15" hidden="1">
+    <row r="907" spans="1:15">
       <c r="A907" t="s">
         <v>1319</v>
       </c>
@@ -31169,7 +31253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="908" spans="1:15" hidden="1">
+    <row r="908" spans="1:15">
       <c r="A908" t="s">
         <v>647</v>
       </c>
@@ -31198,7 +31282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="909" spans="1:15" hidden="1">
+    <row r="909" spans="1:15">
       <c r="A909" t="s">
         <v>1321</v>
       </c>
@@ -31227,7 +31311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="910" spans="1:15" hidden="1">
+    <row r="910" spans="1:15">
       <c r="A910" t="s">
         <v>1323</v>
       </c>
@@ -31256,7 +31340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="911" spans="1:15" hidden="1">
+    <row r="911" spans="1:15">
       <c r="A911" t="s">
         <v>1325</v>
       </c>
@@ -31285,7 +31369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="912" spans="1:15" hidden="1">
+    <row r="912" spans="1:15">
       <c r="A912" t="s">
         <v>1327</v>
       </c>
@@ -31314,7 +31398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="913" spans="1:15" hidden="1">
+    <row r="913" spans="1:15">
       <c r="A913" t="s">
         <v>647</v>
       </c>
@@ -31343,7 +31427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="914" spans="1:15" hidden="1">
+    <row r="914" spans="1:15">
       <c r="A914" t="s">
         <v>1330</v>
       </c>
@@ -31372,7 +31456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="915" spans="1:15" hidden="1">
+    <row r="915" spans="1:15">
       <c r="A915" t="s">
         <v>1332</v>
       </c>
@@ -31401,7 +31485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="916" spans="1:15" hidden="1">
+    <row r="916" spans="1:15">
       <c r="A916" t="s">
         <v>140</v>
       </c>
@@ -31430,7 +31514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="917" spans="1:15" hidden="1">
+    <row r="917" spans="1:15">
       <c r="A917" t="s">
         <v>919</v>
       </c>
@@ -31459,7 +31543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="918" spans="1:15" hidden="1">
+    <row r="918" spans="1:15">
       <c r="A918" t="s">
         <v>1336</v>
       </c>
@@ -31488,7 +31572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="919" spans="1:15" hidden="1">
+    <row r="919" spans="1:15">
       <c r="A919" t="s">
         <v>1338</v>
       </c>
@@ -31517,7 +31601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="920" spans="1:15" hidden="1">
+    <row r="920" spans="1:15">
       <c r="A920" t="s">
         <v>647</v>
       </c>
@@ -31546,7 +31630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="921" spans="1:15" hidden="1">
+    <row r="921" spans="1:15">
       <c r="A921" t="s">
         <v>1017</v>
       </c>
@@ -31575,7 +31659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="922" spans="1:15" hidden="1">
+    <row r="922" spans="1:15">
       <c r="A922" t="s">
         <v>1342</v>
       </c>
@@ -31604,7 +31688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="923" spans="1:15" hidden="1">
+    <row r="923" spans="1:15">
       <c r="A923" t="s">
         <v>1344</v>
       </c>
@@ -31633,7 +31717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="924" spans="1:15" hidden="1">
+    <row r="924" spans="1:15">
       <c r="A924" t="s">
         <v>1180</v>
       </c>
@@ -31662,7 +31746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="925" spans="1:15" hidden="1">
+    <row r="925" spans="1:15">
       <c r="A925" t="s">
         <v>1186</v>
       </c>
@@ -31691,7 +31775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="926" spans="1:15" hidden="1">
+    <row r="926" spans="1:15">
       <c r="A926" t="s">
         <v>527</v>
       </c>
@@ -31720,7 +31804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="927" spans="1:15" hidden="1">
+    <row r="927" spans="1:15">
       <c r="A927" t="s">
         <v>1351</v>
       </c>
@@ -31749,7 +31833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="928" spans="1:15" hidden="1">
+    <row r="928" spans="1:15">
       <c r="A928" t="s">
         <v>1353</v>
       </c>
@@ -31778,7 +31862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="929" spans="1:15" hidden="1">
+    <row r="929" spans="1:15">
       <c r="A929" t="s">
         <v>1356</v>
       </c>
@@ -31807,7 +31891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="930" spans="1:15" hidden="1">
+    <row r="930" spans="1:15">
       <c r="A930" t="s">
         <v>1356</v>
       </c>
@@ -31836,7 +31920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="931" spans="1:15" hidden="1">
+    <row r="931" spans="1:15">
       <c r="A931" t="s">
         <v>156</v>
       </c>
@@ -31865,7 +31949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="932" spans="1:15" hidden="1">
+    <row r="932" spans="1:15">
       <c r="A932" t="s">
         <v>1361</v>
       </c>
@@ -31894,7 +31978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="933" spans="1:15" hidden="1">
+    <row r="933" spans="1:15">
       <c r="A933" t="s">
         <v>1364</v>
       </c>
@@ -31923,7 +32007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="934" spans="1:15" hidden="1">
+    <row r="934" spans="1:15">
       <c r="A934" t="s">
         <v>1366</v>
       </c>
@@ -31952,7 +32036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="935" spans="1:15" hidden="1">
+    <row r="935" spans="1:15">
       <c r="A935" t="s">
         <v>1367</v>
       </c>
@@ -31981,7 +32065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="936" spans="1:15" hidden="1">
+    <row r="936" spans="1:15">
       <c r="A936" t="s">
         <v>1368</v>
       </c>
@@ -32010,7 +32094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="937" spans="1:15" hidden="1">
+    <row r="937" spans="1:15">
       <c r="A937" t="s">
         <v>1371</v>
       </c>
@@ -32039,7 +32123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="938" spans="1:15" hidden="1">
+    <row r="938" spans="1:15">
       <c r="A938" t="s">
         <v>1372</v>
       </c>
@@ -32068,7 +32152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="939" spans="1:15" hidden="1">
+    <row r="939" spans="1:15">
       <c r="A939" t="s">
         <v>193</v>
       </c>
@@ -32097,7 +32181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="940" spans="1:15" hidden="1">
+    <row r="940" spans="1:15">
       <c r="A940" t="s">
         <v>998</v>
       </c>
@@ -32126,7 +32210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="941" spans="1:15" hidden="1">
+    <row r="941" spans="1:15">
       <c r="A941" t="s">
         <v>1375</v>
       </c>
@@ -32155,7 +32239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="942" spans="1:15" hidden="1">
+    <row r="942" spans="1:15">
       <c r="A942" t="s">
         <v>1361</v>
       </c>
@@ -32184,7 +32268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="943" spans="1:15" hidden="1">
+    <row r="943" spans="1:15">
       <c r="A943" t="s">
         <v>1368</v>
       </c>
@@ -32213,7 +32297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="944" spans="1:15" hidden="1">
+    <row r="944" spans="1:15">
       <c r="A944" t="s">
         <v>1378</v>
       </c>
@@ -32242,7 +32326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="945" spans="1:15" hidden="1">
+    <row r="945" spans="1:15">
       <c r="A945" t="s">
         <v>107</v>
       </c>
@@ -32271,7 +32355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="946" spans="1:15" hidden="1">
+    <row r="946" spans="1:15">
       <c r="A946" t="s">
         <v>1380</v>
       </c>
@@ -32300,7 +32384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="947" spans="1:15" hidden="1">
+    <row r="947" spans="1:15">
       <c r="A947" t="s">
         <v>1367</v>
       </c>
@@ -32329,7 +32413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="948" spans="1:15" hidden="1">
+    <row r="948" spans="1:15">
       <c r="A948" t="s">
         <v>949</v>
       </c>
@@ -32358,7 +32442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="949" spans="1:15" hidden="1">
+    <row r="949" spans="1:15">
       <c r="A949" t="s">
         <v>1383</v>
       </c>
@@ -32387,7 +32471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="950" spans="1:15" hidden="1">
+    <row r="950" spans="1:15">
       <c r="A950" t="s">
         <v>310</v>
       </c>
@@ -32416,7 +32500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="951" spans="1:15" hidden="1">
+    <row r="951" spans="1:15">
       <c r="A951" t="s">
         <v>1385</v>
       </c>
@@ -32445,7 +32529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="952" spans="1:15" hidden="1">
+    <row r="952" spans="1:15">
       <c r="A952" t="s">
         <v>1387</v>
       </c>
@@ -32474,7 +32558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="953" spans="1:15" hidden="1">
+    <row r="953" spans="1:15">
       <c r="A953" t="s">
         <v>325</v>
       </c>
@@ -32503,7 +32587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="954" spans="1:15" hidden="1">
+    <row r="954" spans="1:15">
       <c r="A954" t="s">
         <v>1390</v>
       </c>
@@ -32532,7 +32616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="955" spans="1:15" hidden="1">
+    <row r="955" spans="1:15">
       <c r="A955" t="s">
         <v>1392</v>
       </c>
@@ -32561,7 +32645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="956" spans="1:15" hidden="1">
+    <row r="956" spans="1:15">
       <c r="A956" t="s">
         <v>1395</v>
       </c>
@@ -32590,7 +32674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="957" spans="1:15" hidden="1">
+    <row r="957" spans="1:15">
       <c r="A957" t="s">
         <v>1396</v>
       </c>
@@ -32619,7 +32703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="958" spans="1:15" hidden="1">
+    <row r="958" spans="1:15">
       <c r="A958" t="s">
         <v>1398</v>
       </c>
@@ -32648,7 +32732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="959" spans="1:15" hidden="1">
+    <row r="959" spans="1:15">
       <c r="A959" t="s">
         <v>1400</v>
       </c>
@@ -32677,7 +32761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="960" spans="1:15" hidden="1">
+    <row r="960" spans="1:15">
       <c r="A960" t="s">
         <v>1378</v>
       </c>
@@ -32706,7 +32790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="961" spans="1:15" hidden="1">
+    <row r="961" spans="1:15">
       <c r="A961" t="s">
         <v>1403</v>
       </c>
@@ -32735,7 +32819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="962" spans="1:15" hidden="1">
+    <row r="962" spans="1:15">
       <c r="A962" t="s">
         <v>1405</v>
       </c>
@@ -32774,15 +32858,8 @@
       <c r="B968" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P962" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="data authorship"/>
-        <filter val="own data"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="B30:O30 A48:O50 B51:O51 B66:O66 B163:O163 A213:H213 I213:O214 A215:O230 B231:O231 B214:G214 A232:O245 B246:O246 A145:H145 A1:O29 A31:O46 B47:O47 J145:O145 A52:O65 A67:O144 A146:O162 A164:O212 O570:O594 A247:O569 A570:M594 A595:O962">
+  <autoFilter ref="A1:P962" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="B30:O30 A48:O50 B51:O51 B66:O66 B163:O163 A213:H213 I213:O214 A215:O230 B231:O231 B214:G214 A232:O245 B246:O246 A145:H145 A1:O29 A31:O46 B47:O47 J145:O145 A52:O65 A67:O144 A146:O162 A164:O212 O570:O594 A595:O962 A247:O569 A570:M594">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>$O1=TRUE</formula>
     </cfRule>
@@ -32802,12 +32879,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100029FD0B41DD07841BED16965712E158C" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e0f1011f30fef6dde8223745cec2fc96">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aaacefca-f467-416c-abd0-2b181dff1e20" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4d5cb4cdee1db726a521ed27371901b5" ns2:_="">
     <xsd:import namespace="aaacefca-f467-416c-abd0-2b181dff1e20"/>
@@ -32951,6 +33022,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -32961,13 +33038,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45D27483-4B25-4C13-ADD2-2FFF45E1670E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62DB5D2C-15B8-4357-A22A-D88F7291A956}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="aaacefca-f467-416c-abd0-2b181dff1e20"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62DB5D2C-15B8-4357-A22A-D88F7291A956}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45D27483-4B25-4C13-ADD2-2FFF45E1670E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B07315CF-E1D2-41BC-97DE-837096B66448}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B07315CF-E1D2-41BC-97DE-837096B66448}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/verification/datastet_and_added_summarised/datastet_and_added_filled_raw/charite_dois_ids_distinct_v9.xlsx
+++ b/data/verification/datastet_and_added_summarised/datastet_and_added_filled_raw/charite_dois_ids_distinct_v9.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29318"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AVIHAY\git\DCC-v3\data\verification\datastet_and_added_summarised\datastet_and_added_filled_raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://charitede.sharepoint.com/sites/TeamOpenDataundForschungsdatenmanagement/Shared Documents/DCC analysis/datastet and added identifiers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3322BA5-DB1C-451A-957B-0E41A0843540}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2695" documentId="11_57DF80A4F9203448D8892CCCE483C471B2B16C48" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D336E1B8-7CFE-4B50-A261-1C7CA944C819}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,10 +28,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6824" uniqueCount="1408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6869" uniqueCount="1421">
   <si>
     <t>doi_datastet_and_added</t>
   </si>
@@ -4263,6 +4263,45 @@
   </si>
   <si>
     <t>code cannot be found in the publication</t>
+  </si>
+  <si>
+    <t>10.17863/cam.23511</t>
+  </si>
+  <si>
+    <t>University of Cambridge Repository</t>
+  </si>
+  <si>
+    <t>CC BY</t>
+  </si>
+  <si>
+    <t>10.1242/dev.201228</t>
+  </si>
+  <si>
+    <t>10.17863/cam.87955</t>
+  </si>
+  <si>
+    <t>not in DAS</t>
+  </si>
+  <si>
+    <t>10.1038/s41467-020-16929-8</t>
+  </si>
+  <si>
+    <t>10.5281/zenodo.2529950</t>
+  </si>
+  <si>
+    <t>Zenodo</t>
+  </si>
+  <si>
+    <t>10.1016/j.cortex.2021.08.002</t>
+  </si>
+  <si>
+    <t>10.6084/m9.figshare.915436</t>
+  </si>
+  <si>
+    <t>figshare</t>
+  </si>
+  <si>
+    <t>10.1016/j.nicl.2020.102536</t>
   </si>
 </sst>
 </file>
@@ -4348,9 +4387,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -4386,9 +4432,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4426,9 +4472,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4461,26 +4507,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4513,26 +4542,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4706,7 +4718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P968"/>
+  <dimension ref="A1:P967"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.28515625" bestFit="1" customWidth="1"/>
@@ -32848,30 +32860,192 @@
         <v>0</v>
       </c>
     </row>
+    <row r="963" spans="1:15">
+      <c r="A963" t="s">
+        <v>68</v>
+      </c>
+      <c r="B963" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C963" t="s">
+        <v>17</v>
+      </c>
+      <c r="D963" t="s">
+        <v>35</v>
+      </c>
+      <c r="E963" s="1">
+        <v>45924</v>
+      </c>
+      <c r="F963" t="s">
+        <v>20</v>
+      </c>
+      <c r="G963" t="s">
+        <v>20</v>
+      </c>
+      <c r="H963" t="s">
+        <v>1409</v>
+      </c>
+      <c r="I963" t="s">
+        <v>20</v>
+      </c>
+      <c r="J963" t="s">
+        <v>20</v>
+      </c>
+      <c r="K963" t="s">
+        <v>31</v>
+      </c>
+      <c r="L963" t="s">
+        <v>1410</v>
+      </c>
+      <c r="M963" t="s">
+        <v>20</v>
+      </c>
+      <c r="N963">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="964" spans="1:15">
+      <c r="A964" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B964" s="7" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C964" t="s">
+        <v>17</v>
+      </c>
+      <c r="D964" t="s">
+        <v>35</v>
+      </c>
+      <c r="E964" s="1">
+        <v>45924</v>
+      </c>
+      <c r="F964" t="s">
+        <v>20</v>
+      </c>
+      <c r="G964" t="s">
+        <v>20</v>
+      </c>
+      <c r="H964" t="s">
+        <v>1409</v>
+      </c>
+      <c r="I964" t="s">
+        <v>1413</v>
+      </c>
+      <c r="J964" t="s">
+        <v>31</v>
+      </c>
+      <c r="K964" t="s">
+        <v>31</v>
+      </c>
+      <c r="L964" t="s">
+        <v>1410</v>
+      </c>
+      <c r="M964" t="s">
+        <v>20</v>
+      </c>
+      <c r="N964">
+        <v>2023</v>
+      </c>
+    </row>
     <row r="965" spans="1:15">
-      <c r="B965" s="7"/>
+      <c r="A965" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B965" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C965" t="s">
+        <v>17</v>
+      </c>
+      <c r="D965" t="s">
+        <v>35</v>
+      </c>
+      <c r="E965" s="1">
+        <v>45924</v>
+      </c>
+      <c r="F965" t="s">
+        <v>19</v>
+      </c>
+      <c r="G965" t="s">
+        <v>100</v>
+      </c>
+      <c r="H965" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="966" spans="1:15">
+      <c r="A966" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B966" s="7" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C966" t="s">
+        <v>17</v>
+      </c>
+      <c r="D966" t="s">
+        <v>35</v>
+      </c>
+      <c r="E966" s="1">
+        <v>45924</v>
+      </c>
+      <c r="F966" t="s">
+        <v>19</v>
+      </c>
+      <c r="G966" t="s">
+        <v>100</v>
+      </c>
+      <c r="H966" t="s">
+        <v>1419</v>
+      </c>
     </row>
     <row r="967" spans="1:15">
-      <c r="B967" s="7"/>
-    </row>
-    <row r="968" spans="1:15">
-      <c r="B968" s="7"/>
+      <c r="A967" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B967" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C967" t="s">
+        <v>17</v>
+      </c>
+      <c r="D967" t="s">
+        <v>35</v>
+      </c>
+      <c r="E967" s="1">
+        <v>45924</v>
+      </c>
+      <c r="F967" t="s">
+        <v>19</v>
+      </c>
+      <c r="G967" t="s">
+        <v>100</v>
+      </c>
+      <c r="H967" t="s">
+        <v>1419</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:P962" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="B30:O30 A48:O50 B51:O51 B66:O66 B163:O163 A213:H213 I213:O214 A215:O230 B231:O231 B214:G214 A232:O245 B246:O246 A145:H145 A1:O29 A31:O46 B47:O47 J145:O145 A52:O65 A67:O144 A146:O162 A164:O212 O570:O594 A595:O962 A247:O569 A570:M594">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>$O1=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H214">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>$O213=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N582:N594">
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="1" priority="6">
       <formula>$O570=TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E963:E967">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$O963=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -32879,9 +33053,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100029FD0B41DD07841BED16965712E158C" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e0f1011f30fef6dde8223745cec2fc96">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aaacefca-f467-416c-abd0-2b181dff1e20" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4d5cb4cdee1db726a521ed27371901b5" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100029FD0B41DD07841BED16965712E158C" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ae6d51e96c8c66a8de8dfe8311f95192">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aaacefca-f467-416c-abd0-2b181dff1e20" xmlns:ns3="a0e84d40-090a-490d-8a02-2942ffba970a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f9e171e4f7fb14517da8847a2c60885" ns2:_="" ns3:_="">
     <xsd:import namespace="aaacefca-f467-416c-abd0-2b181dff1e20"/>
+    <xsd:import namespace="a0e84d40-090a-490d-8a02-2942ffba970a"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -32892,6 +33067,12 @@
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -32921,6 +33102,50 @@
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="14" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2375ea7b-1eef-4e91-915e-32e4cb5a9c34" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a0e84d40-090a-490d-8a02-2942ffba970a" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="15" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b1b93042-dae5-4a91-aee7-e8b26f1570c8}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="a0e84d40-090a-490d-8a02-2942ffba970a">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -33023,12 +33248,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -33037,37 +33256,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a0e84d40-090a-490d-8a02-2942ffba970a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaacefca-f467-416c-abd0-2b181dff1e20">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62DB5D2C-15B8-4357-A22A-D88F7291A956}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="aaacefca-f467-416c-abd0-2b181dff1e20"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2C5B169-AEF7-4447-855E-125D156E9E64}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45D27483-4B25-4C13-ADD2-2FFF45E1670E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B07315CF-E1D2-41BC-97DE-837096B66448}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B07315CF-E1D2-41BC-97DE-837096B66448}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45D27483-4B25-4C13-ADD2-2FFF45E1670E}"/>
 </file>